--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -12,14 +12,9 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="iniciativa" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -113,11 +108,9 @@
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -141,13 +134,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -181,34 +174,34 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -492,14 +485,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
     <col min="3" max="4" width="17.28515625" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" customWidth="1"/>
     <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" customWidth="1"/>
@@ -511,60 +504,60 @@
     <col min="18" max="18" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="5" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>9445721</v>
       </c>
@@ -599,7 +592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>9452379</v>
       </c>
@@ -652,7 +645,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>9452379</v>
       </c>
@@ -705,7 +698,7 @@
         <v>140092199.68000001</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>9456627</v>
       </c>
@@ -758,7 +751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>9468055</v>
       </c>
@@ -811,7 +804,7 @@
         <v>132217.76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>9468055</v>
       </c>
@@ -864,7 +857,7 @@
         <v>103278.19</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>9468055</v>
       </c>
@@ -917,7 +910,7 @@
         <v>168403.88</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9468055</v>
       </c>
@@ -970,7 +963,7 @@
         <v>1205684.9099999999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>9468055</v>
       </c>
@@ -1023,7 +1016,7 @@
         <v>181664.85</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>9468057</v>
       </c>
@@ -1076,7 +1069,7 @@
         <v>3016850.76</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>9470658</v>
       </c>
@@ -1129,7 +1122,7 @@
         <v>664996.21</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>9473170</v>
       </c>
@@ -1182,7 +1175,7 @@
         <v>538743.04000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>9473171</v>
       </c>
@@ -1235,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>9474703</v>
       </c>
@@ -1288,7 +1281,7 @@
         <v>78057584.670000002</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>9480259</v>
       </c>
@@ -1323,7 +1316,7 @@
         <v>4156312.7</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>9493230</v>
       </c>
@@ -1358,8 +1351,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:17" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Documents\portal_mariana\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E8923EA-7588-43B6-85C8-BEB25D0FA142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="iniciativa" sheetId="1" r:id="rId1"/>
+    <sheet name="orgao" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -102,7 +103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
@@ -116,13 +117,11 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF6500"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -232,39 +231,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -297,9 +296,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -332,6 +348,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -393,13 +426,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -408,6 +434,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -472,18 +505,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Documents\portal_mariana\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E8923EA-7588-43B6-85C8-BEB25D0FA142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E789D10F-337A-4D13-8854-D03EF52F8EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19965" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="720" windowWidth="18435" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -20,26 +20,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
-  <si>
-    <t>ContratoConvênio Entrada</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
-  </si>
-  <si>
-    <t>Valor Despesa Empenhada</t>
-  </si>
-  <si>
-    <t>Valor Despesa Liquidada</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <si>
+    <t>Iniciativa</t>
+  </si>
+  <si>
+    <t>Código Órgão</t>
+  </si>
+  <si>
+    <t>Nome Órgão</t>
+  </si>
+  <si>
+    <t>Valor Empenhado</t>
+  </si>
+  <si>
+    <t>Valor Liquidado</t>
   </si>
   <si>
     <t>Valor Pago Financeiro</t>
   </si>
   <si>
+    <t>Valor Liquidado RP</t>
+  </si>
+  <si>
     <t>Valor Cancelado Processado</t>
   </si>
   <si>
@@ -52,10 +55,10 @@
     <t>Valor Restabelecido Não Processado</t>
   </si>
   <si>
-    <t>VALOR CANCELADO EM RESTOA A PAGAR [(8+9)-(10+11)]</t>
-  </si>
-  <si>
-    <t>VALOR EMPENHADO EFETIVO (4 - 12)</t>
+    <t>Valor Cancelado RP</t>
+  </si>
+  <si>
+    <t>Valor Empenhado Efetivo</t>
   </si>
   <si>
     <t>Valor Pago Processado</t>
@@ -64,10 +67,10 @@
     <t>Valor Pago Não Processado</t>
   </si>
   <si>
-    <t xml:space="preserve">VALOR PAGO EM RESTOS A PAGAR (14 + 15) </t>
-  </si>
-  <si>
-    <t>VALOR PAGO TOTAL ( 6 +16)</t>
+    <t>Valor Pago RP</t>
+  </si>
+  <si>
+    <t>Valor Pago Total</t>
   </si>
   <si>
     <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
@@ -117,11 +120,13 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF6500"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -542,10 +547,9 @@
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
+    <col min="3" max="5" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" customWidth="1"/>
@@ -557,7 +561,7 @@
     <col min="18" max="18" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,37 +581,37 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -618,7 +622,7 @@
         <v>1231</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="8">
         <v>9350820</v>
@@ -653,7 +657,7 @@
         <v>1491</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="8">
         <v>5000000</v>
@@ -706,16 +710,16 @@
         <v>2301</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="8">
         <v>193141925.59999999</v>
       </c>
       <c r="E4" s="8">
-        <v>129411502.38</v>
+        <v>131330886.51000001</v>
       </c>
       <c r="F4" s="8">
-        <v>119456878.62</v>
+        <v>123027497.59999999</v>
       </c>
       <c r="G4" s="8">
         <v>15780164.470000001</v>
@@ -748,7 +752,7 @@
         <v>20635321.059999999</v>
       </c>
       <c r="Q4" s="10">
-        <v>140092199.68000001</v>
+        <v>143662818.66</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -759,7 +763,7 @@
         <v>1401</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="8">
         <v>2400949</v>
@@ -812,10 +816,10 @@
         <v>1221</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="8">
-        <v>169064.12</v>
+        <v>200389.18</v>
       </c>
       <c r="E6" s="8">
         <v>125087.45</v>
@@ -842,7 +846,7 @@
         <v>9651.6</v>
       </c>
       <c r="M6" s="10">
-        <v>159412.51999999999</v>
+        <v>190737.58</v>
       </c>
       <c r="N6" s="9">
         <v>0</v>
@@ -865,7 +869,7 @@
         <v>1231</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="8">
         <v>216624.1</v>
@@ -918,7 +922,7 @@
         <v>1481</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8">
         <v>245978.79</v>
@@ -971,16 +975,16 @@
         <v>1501</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="8">
-        <v>2494582.33</v>
+        <v>2495612.89</v>
       </c>
       <c r="E9" s="8">
-        <v>1363096.89</v>
+        <v>1364127.45</v>
       </c>
       <c r="F9" s="8">
-        <v>937064.85</v>
+        <v>938095.41</v>
       </c>
       <c r="G9" s="8">
         <v>302674.08</v>
@@ -1001,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>2494582.33</v>
+        <v>2495612.89</v>
       </c>
       <c r="N9" s="9">
         <v>12856.3</v>
@@ -1013,7 +1017,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q9" s="10">
-        <v>1205684.9099999999</v>
+        <v>1206715.47</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1024,7 +1028,7 @@
         <v>4251</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="8">
         <v>304289.25</v>
@@ -1077,7 +1081,7 @@
         <v>1371</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="8">
         <v>3574888.61</v>
@@ -1130,7 +1134,7 @@
         <v>1231</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="8">
         <v>2592199.31</v>
@@ -1183,7 +1187,7 @@
         <v>2301</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="8">
         <v>736365.61</v>
@@ -1236,7 +1240,7 @@
         <v>1221</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="8">
         <v>10161911</v>
@@ -1289,7 +1293,7 @@
         <v>1231</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8">
         <v>79058892.349999994</v>
@@ -1342,7 +1346,7 @@
         <v>1221</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="8">
         <v>4223525</v>
@@ -1377,7 +1381,7 @@
         <v>1071</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" s="8">
         <v>3500000</v>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Documents\portal_mariana\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E789D10F-337A-4D13-8854-D03EF52F8EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8641D1FA-B816-475C-9CBF-F43B740595EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="720" windowWidth="18435" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="720" windowWidth="19965" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
-    <t>Iniciativa</t>
+    <t>Código Iniciativa</t>
   </si>
   <si>
     <t>Código Órgão</t>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -1,26 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Documents\portal_mariana\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_mariana\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8641D1FA-B816-475C-9CBF-F43B740595EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="720" windowWidth="19965" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420"/>
   </bookViews>
   <sheets>
-    <sheet name="orgao" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>Código Iniciativa</t>
   </si>
@@ -106,27 +110,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF6500"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -138,13 +142,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -178,34 +182,34 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -236,39 +240,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -301,26 +305,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -353,23 +340,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -431,6 +401,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -439,13 +416,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -510,40 +480,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
@@ -561,67 +511,67 @@
     <col min="18" max="18" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+    <row r="2" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>9445721</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <v>1231</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="8">
@@ -649,14 +599,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
         <v>9452379</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>1491</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="8">
@@ -702,14 +652,14 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>9452379</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>2301</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="8">
@@ -719,7 +669,7 @@
         <v>131330886.51000001</v>
       </c>
       <c r="F4" s="8">
-        <v>123027497.59999999</v>
+        <v>123971038.95</v>
       </c>
       <c r="G4" s="8">
         <v>15780164.470000001</v>
@@ -752,17 +702,17 @@
         <v>20635321.059999999</v>
       </c>
       <c r="Q4" s="10">
-        <v>143662818.66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+        <v>144606360.00999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>9456627</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>1401</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="8">
@@ -808,14 +758,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>9468055</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>1221</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="8">
@@ -861,24 +811,24 @@
         <v>132217.76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+    <row r="7" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>9468055</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>1231</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="8">
         <v>216624.1</v>
       </c>
       <c r="E7" s="8">
-        <v>122189.98</v>
+        <v>153457.43</v>
       </c>
       <c r="F7" s="8">
-        <v>79555.399999999994</v>
+        <v>105979.8</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -911,17 +861,17 @@
         <v>23722.79</v>
       </c>
       <c r="Q7" s="10">
-        <v>103278.19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+        <v>129702.59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>9468055</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>1481</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="8">
@@ -967,18 +917,18 @@
         <v>168403.88</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
+    <row r="9" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>9468055</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="3">
         <v>1501</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="8">
-        <v>2495612.89</v>
+        <v>2948730.86</v>
       </c>
       <c r="E9" s="8">
         <v>1364127.45</v>
@@ -1005,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>2495612.89</v>
+        <v>2948730.86</v>
       </c>
       <c r="N9" s="9">
         <v>12856.3</v>
@@ -1020,14 +970,14 @@
         <v>1206715.47</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
+    <row r="10" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>9468055</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>4251</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8">
@@ -1073,18 +1023,18 @@
         <v>181664.85</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
+    <row r="11" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>9468057</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>1371</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="8">
-        <v>3574888.61</v>
+        <v>4575233.59</v>
       </c>
       <c r="E11" s="8">
         <v>3009446.64</v>
@@ -1111,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="10">
-        <v>3574888.61</v>
+        <v>4575233.59</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -1126,14 +1076,14 @@
         <v>3016850.76</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+    <row r="12" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>9470658</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>1231</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="8">
@@ -1146,7 +1096,7 @@
         <v>296909.12</v>
       </c>
       <c r="G12" s="8">
-        <v>382245.71</v>
+        <v>419950.5</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1170,23 +1120,23 @@
         <v>0</v>
       </c>
       <c r="O12" s="9">
-        <v>368087.09</v>
+        <v>405791.88</v>
       </c>
       <c r="P12" s="10">
-        <v>368087.09</v>
+        <v>405791.88</v>
       </c>
       <c r="Q12" s="10">
-        <v>664996.21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
+        <v>702701</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>9473170</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="3">
         <v>2301</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="8">
@@ -1232,14 +1182,14 @@
         <v>538743.04000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>9473171</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="3">
         <v>1221</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="8">
@@ -1285,14 +1235,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
+    <row r="15" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>9474703</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="3">
         <v>1231</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="8">
@@ -1338,24 +1288,24 @@
         <v>78057584.670000002</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
+    <row r="16" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>9480259</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="3">
         <v>1221</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="8">
         <v>4223525</v>
       </c>
       <c r="E16" s="8">
-        <v>4156312.7</v>
+        <v>4156674.7</v>
       </c>
       <c r="F16" s="8">
-        <v>4156312.7</v>
+        <v>4156674.7</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="9"/>
@@ -1370,17 +1320,17 @@
       <c r="O16" s="9"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="10">
-        <v>4156312.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
+        <v>4156674.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>9493230</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="3">
         <v>1071</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="8">
@@ -1408,10 +1358,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>9493391</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1071</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="8">
+        <v>11399338.199999999</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10">
+        <v>11399338.199999999</v>
+      </c>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -112,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,###,###,###,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -185,6 +185,15 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -194,19 +203,10 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -511,7 +511,7 @@
     <col min="18" max="18" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,45 +533,45 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
         <v>9445721</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6">
         <v>1231</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="8">
@@ -599,14 +599,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+    <row r="3" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
         <v>9452379</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>1491</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="8">
@@ -652,14 +652,14 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
         <v>9452379</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>2301</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="8">
@@ -705,14 +705,14 @@
         <v>144606360.00999999</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>9456627</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>1401</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="8">
@@ -758,14 +758,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>9468055</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>1221</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="8">
@@ -811,14 +811,14 @@
         <v>132217.76</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>9468055</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>1231</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="8">
@@ -864,14 +864,14 @@
         <v>129702.59</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>9468055</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="6">
         <v>1481</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="8">
@@ -917,21 +917,21 @@
         <v>168403.88</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
         <v>9468055</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="6">
         <v>1501</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="8">
-        <v>2948730.86</v>
+        <v>2946730.86</v>
       </c>
       <c r="E9" s="8">
-        <v>1364127.45</v>
+        <v>1716012.47</v>
       </c>
       <c r="F9" s="8">
         <v>938095.41</v>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>2948730.86</v>
+        <v>2946730.86</v>
       </c>
       <c r="N9" s="9">
         <v>12856.3</v>
@@ -970,14 +970,14 @@
         <v>1206715.47</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <v>9468055</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="6">
         <v>4251</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8">
@@ -1023,21 +1023,21 @@
         <v>181664.85</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>9468057</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="6">
         <v>1371</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="8">
         <v>4575233.59</v>
       </c>
       <c r="E11" s="8">
-        <v>3009446.64</v>
+        <v>3748679.43</v>
       </c>
       <c r="F11" s="8">
         <v>2539910.5</v>
@@ -1076,14 +1076,14 @@
         <v>3016850.76</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>9470658</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="6">
         <v>1231</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="8">
@@ -1129,14 +1129,14 @@
         <v>702701</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>9473170</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="6">
         <v>2301</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="8">
@@ -1182,18 +1182,18 @@
         <v>538743.04000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>9473171</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="6">
         <v>1221</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="8">
-        <v>10161911</v>
+        <v>10857754.93</v>
       </c>
       <c r="E14" s="8">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="10">
-        <v>10161911</v>
+        <v>10857754.93</v>
       </c>
       <c r="N14" s="9">
         <v>0</v>
@@ -1235,14 +1235,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>9474703</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="6">
         <v>1231</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="8">
@@ -1288,14 +1288,14 @@
         <v>78057584.670000002</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>9480259</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="6">
         <v>1221</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="8">
@@ -1323,14 +1323,14 @@
         <v>4156674.7</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>9493230</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="6">
         <v>1071</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="8">
@@ -1358,14 +1358,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>9493391</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="6">
         <v>1071</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="8">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -5,26 +5,21 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_mariana\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="orgao" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Código Iniciativa</t>
   </si>
@@ -77,6 +72,12 @@
     <t>Valor Pago Total</t>
   </si>
   <si>
+    <t>FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
     <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
   </si>
   <si>
@@ -96,9 +97,6 @@
   </si>
   <si>
     <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
   </si>
   <si>
     <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
@@ -116,11 +114,9 @@
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -142,13 +138,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7F7F7"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF7F7F7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -182,34 +178,34 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -492,8 +488,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
@@ -511,74 +507,74 @@
     <col min="18" max="18" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="5" customFormat="1" ht="36" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>9445721</v>
+        <v>9445683</v>
       </c>
       <c r="B2" s="6">
-        <v>1231</v>
+        <v>4291</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="8">
-        <v>9350820</v>
+        <v>150400857</v>
       </c>
       <c r="E2" s="8">
-        <v>0</v>
+        <v>13904760</v>
       </c>
       <c r="F2" s="8">
         <v>0</v>
@@ -590,7 +586,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10">
-        <v>9350820</v>
+        <v>150400857</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -599,127 +595,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
-        <v>9452379</v>
+        <v>9445718</v>
       </c>
       <c r="B3" s="6">
-        <v>1491</v>
+        <v>4251</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="8">
-        <v>5000000</v>
+        <v>4000</v>
       </c>
       <c r="E3" s="8">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
       </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="10">
-        <v>5000000</v>
-      </c>
-      <c r="N3" s="9">
-        <v>2500000</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="10">
-        <v>2500000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="10"/>
       <c r="Q3" s="10">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
-        <v>9452379</v>
+        <v>9445721</v>
       </c>
       <c r="B4" s="6">
-        <v>2301</v>
+        <v>1231</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="8">
-        <v>193141925.59999999</v>
+        <v>9350820</v>
       </c>
       <c r="E4" s="8">
-        <v>131330886.51000001</v>
+        <v>0</v>
       </c>
       <c r="F4" s="8">
-        <v>123971038.95</v>
-      </c>
-      <c r="G4" s="8">
-        <v>15780164.470000001</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>10601950.529999999</v>
-      </c>
-      <c r="K4" s="9">
-        <v>23767.08</v>
-      </c>
-      <c r="L4" s="10">
-        <v>10625717.609999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10"/>
       <c r="M4" s="10">
-        <v>182516207.99000001</v>
-      </c>
-      <c r="N4" s="9">
-        <v>5029440.01</v>
-      </c>
-      <c r="O4" s="9">
-        <v>15605881.050000001</v>
-      </c>
-      <c r="P4" s="10">
-        <v>20635321.059999999</v>
-      </c>
+        <v>9350820</v>
+      </c>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
       <c r="Q4" s="10">
-        <v>144606360.00999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
-        <v>9456627</v>
+        <v>9452379</v>
       </c>
       <c r="B5" s="6">
-        <v>1401</v>
+        <v>1491</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="8">
-        <v>2400949</v>
+        <v>5000000</v>
       </c>
       <c r="E5" s="8">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="F5" s="8">
         <v>0</v>
@@ -743,42 +703,42 @@
         <v>0</v>
       </c>
       <c r="M5" s="10">
-        <v>2400949</v>
+        <v>5000000</v>
       </c>
       <c r="N5" s="9">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="O5" s="9">
         <v>0</v>
       </c>
       <c r="P5" s="10">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="Q5" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
-        <v>9468055</v>
+        <v>9452379</v>
       </c>
       <c r="B6" s="6">
-        <v>1221</v>
+        <v>2301</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="8">
-        <v>200389.18</v>
+        <v>211141913.41999999</v>
       </c>
       <c r="E6" s="8">
-        <v>125087.45</v>
+        <v>131342254.28</v>
       </c>
       <c r="F6" s="8">
-        <v>105744.86</v>
+        <v>124923849.11</v>
       </c>
       <c r="G6" s="8">
-        <v>31325.06</v>
+        <v>15780164.470000001</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -787,51 +747,51 @@
         <v>0</v>
       </c>
       <c r="J6" s="9">
-        <v>9651.6</v>
+        <v>10601950.529999999</v>
       </c>
       <c r="K6" s="9">
-        <v>0</v>
+        <v>23767.08</v>
       </c>
       <c r="L6" s="10">
-        <v>9651.6</v>
+        <v>10625717.609999999</v>
       </c>
       <c r="M6" s="10">
-        <v>190737.58</v>
+        <v>200516195.81</v>
       </c>
       <c r="N6" s="9">
-        <v>0</v>
+        <v>5029440.01</v>
       </c>
       <c r="O6" s="9">
-        <v>26472.9</v>
+        <v>15605881.050000001</v>
       </c>
       <c r="P6" s="10">
-        <v>26472.9</v>
+        <v>20635321.059999999</v>
       </c>
       <c r="Q6" s="10">
-        <v>132217.76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>145559170.16999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
-        <v>9468055</v>
+        <v>9456627</v>
       </c>
       <c r="B7" s="6">
-        <v>1231</v>
+        <v>1401</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D7" s="8">
-        <v>216624.1</v>
+        <v>2400949</v>
       </c>
       <c r="E7" s="8">
-        <v>153457.43</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8">
-        <v>105979.8</v>
+        <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -849,42 +809,42 @@
         <v>0</v>
       </c>
       <c r="M7" s="10">
-        <v>216624.1</v>
+        <v>2400949</v>
       </c>
       <c r="N7" s="9">
-        <v>23722.79</v>
+        <v>0</v>
       </c>
       <c r="O7" s="9">
         <v>0</v>
       </c>
       <c r="P7" s="10">
-        <v>23722.79</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="10">
-        <v>129702.59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>9468055</v>
       </c>
       <c r="B8" s="6">
-        <v>1481</v>
+        <v>1221</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="8">
-        <v>245978.79</v>
+        <v>200389.18</v>
       </c>
       <c r="E8" s="8">
-        <v>152836.49</v>
+        <v>156412.51</v>
       </c>
       <c r="F8" s="8">
-        <v>129204.08</v>
+        <v>132217.76</v>
       </c>
       <c r="G8" s="8">
-        <v>44810.879999999997</v>
+        <v>31325.06</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -893,51 +853,51 @@
         <v>0</v>
       </c>
       <c r="J8" s="9">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="10">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="M8" s="10">
-        <v>245978.79</v>
+        <v>190737.58</v>
       </c>
       <c r="N8" s="9">
-        <v>1339.42</v>
+        <v>0</v>
       </c>
       <c r="O8" s="9">
-        <v>37860.379999999997</v>
+        <v>26472.9</v>
       </c>
       <c r="P8" s="10">
-        <v>39199.800000000003</v>
+        <v>26472.9</v>
       </c>
       <c r="Q8" s="10">
-        <v>168403.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>158690.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9468055</v>
       </c>
       <c r="B9" s="6">
-        <v>1501</v>
+        <v>1231</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>2946730.86</v>
+        <v>216624.1</v>
       </c>
       <c r="E9" s="8">
-        <v>1716012.47</v>
+        <v>153457.43</v>
       </c>
       <c r="F9" s="8">
-        <v>938095.41</v>
+        <v>105979.8</v>
       </c>
       <c r="G9" s="8">
-        <v>302674.08</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -955,42 +915,42 @@
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>2946730.86</v>
+        <v>216624.1</v>
       </c>
       <c r="N9" s="9">
-        <v>12856.3</v>
+        <v>23722.79</v>
       </c>
       <c r="O9" s="9">
-        <v>255763.76</v>
+        <v>0</v>
       </c>
       <c r="P9" s="10">
-        <v>268620.06</v>
+        <v>23722.79</v>
       </c>
       <c r="Q9" s="10">
-        <v>1206715.47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>129702.59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>9468055</v>
       </c>
       <c r="B10" s="6">
-        <v>4251</v>
+        <v>1481</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="8">
-        <v>304289.25</v>
+        <v>292917.3</v>
       </c>
       <c r="E10" s="8">
-        <v>169513.73</v>
+        <v>199873.18</v>
       </c>
       <c r="F10" s="8">
-        <v>141955.49</v>
+        <v>129204.08</v>
       </c>
       <c r="G10" s="8">
-        <v>46987.59</v>
+        <v>44810.879999999997</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1008,374 +968,410 @@
         <v>0</v>
       </c>
       <c r="M10" s="10">
-        <v>304289.25</v>
+        <v>292917.3</v>
       </c>
       <c r="N10" s="9">
-        <v>0</v>
+        <v>1339.42</v>
       </c>
       <c r="O10" s="9">
-        <v>39709.360000000001</v>
+        <v>37860.379999999997</v>
       </c>
       <c r="P10" s="10">
-        <v>39709.360000000001</v>
+        <v>39199.800000000003</v>
       </c>
       <c r="Q10" s="10">
-        <v>181664.85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+        <v>168403.88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
-        <v>9468057</v>
+        <v>9468055</v>
       </c>
       <c r="B11" s="6">
-        <v>1371</v>
+        <v>1501</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="8">
+        <v>2949530.86</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1716012.47</v>
+      </c>
+      <c r="F11" s="8">
+        <v>938095.41</v>
+      </c>
+      <c r="G11" s="8">
+        <v>302674.08</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10">
+        <v>2949530.86</v>
+      </c>
+      <c r="N11" s="9">
+        <v>12856.3</v>
+      </c>
+      <c r="O11" s="9">
+        <v>255763.76</v>
+      </c>
+      <c r="P11" s="10">
+        <v>268620.06</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>1206715.47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>9468055</v>
+      </c>
+      <c r="B12" s="6">
+        <v>4251</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="8">
+        <v>304289.25</v>
+      </c>
+      <c r="E12" s="8">
+        <v>216550.42</v>
+      </c>
+      <c r="F12" s="8">
+        <v>141955.49</v>
+      </c>
+      <c r="G12" s="8">
+        <v>46987.59</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>304289.25</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>39709.360000000001</v>
+      </c>
+      <c r="P12" s="10">
+        <v>39709.360000000001</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>181664.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>9468057</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1371</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="8">
         <v>4575233.59</v>
       </c>
-      <c r="E11" s="8">
-        <v>3748679.43</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="E13" s="8">
+        <v>4009791.62</v>
+      </c>
+      <c r="F13" s="8">
         <v>2539910.5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G13" s="8">
         <v>565340.29</v>
       </c>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
         <v>4575233.59</v>
       </c>
-      <c r="N11" s="9">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
         <v>476940.26</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P13" s="10">
         <v>476940.26</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q13" s="10">
         <v>3016850.76</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>9470658</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B14" s="6">
         <v>1231</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="8">
         <v>2592199.31</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E14" s="8">
         <v>296909.12</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F14" s="8">
         <v>296909.12</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G14" s="8">
         <v>419950.5</v>
       </c>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
         <v>35398.54</v>
       </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
         <v>35398.54</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M14" s="10">
         <v>2556800.77</v>
       </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9">
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
         <v>405791.88</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P14" s="10">
         <v>405791.88</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q14" s="10">
         <v>702701</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>9473170</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B15" s="6">
         <v>2301</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="C15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="8">
         <v>736365.61</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E15" s="8">
         <v>350401.39</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F15" s="8">
         <v>350401.39</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G15" s="8">
         <v>188341.65</v>
       </c>
-      <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9">
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
         <v>197622.57</v>
       </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
         <v>197622.57</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M15" s="10">
         <v>538743.04000000004</v>
       </c>
-      <c r="N13" s="9">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9">
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
         <v>188341.65</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P15" s="10">
         <v>188341.65</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q15" s="10">
         <v>538743.04000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>9473171</v>
-      </c>
-      <c r="B14" s="6">
-        <v>1221</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="8">
-        <v>10857754.93</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0</v>
-      </c>
-      <c r="M14" s="10">
-        <v>10857754.93</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9">
-        <v>0</v>
-      </c>
-      <c r="P14" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
-        <v>9474703</v>
-      </c>
-      <c r="B15" s="6">
-        <v>1231</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="8">
-        <v>79058892.349999994</v>
-      </c>
-      <c r="E15" s="8">
-        <v>78541892.260000005</v>
-      </c>
-      <c r="F15" s="8">
-        <v>77547634.670000002</v>
-      </c>
-      <c r="G15" s="8">
-        <v>517000</v>
-      </c>
-      <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="9">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10">
-        <v>79058892.349999994</v>
-      </c>
-      <c r="N15" s="9">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9">
-        <v>509950</v>
-      </c>
-      <c r="P15" s="10">
-        <v>509950</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>78057584.670000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
-        <v>9480259</v>
       </c>
       <c r="B16" s="6">
         <v>1221</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="8">
-        <v>4223525</v>
+        <v>11495511.93</v>
       </c>
       <c r="E16" s="8">
+        <v>58086.92</v>
+      </c>
+      <c r="F16" s="8">
+        <v>58086.92</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>11495511.93</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="9">
+        <v>0</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>58086.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
+        <v>9474703</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1231</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="8">
+        <v>79058892.349999994</v>
+      </c>
+      <c r="E17" s="8">
+        <v>78541892.260000005</v>
+      </c>
+      <c r="F17" s="8">
+        <v>77547634.670000002</v>
+      </c>
+      <c r="G17" s="8">
+        <v>517000</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>79058892.349999994</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="9">
+        <v>509950</v>
+      </c>
+      <c r="P17" s="10">
+        <v>509950</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>78057584.670000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
+        <v>9480259</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1221</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="8">
+        <v>4313807.5999999996</v>
+      </c>
+      <c r="E18" s="8">
         <v>4156674.7</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F18" s="8">
         <v>4156674.7</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10">
-        <v>4223525</v>
-      </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10">
-        <v>4156674.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
-        <v>9493230</v>
-      </c>
-      <c r="B17" s="6">
-        <v>1071</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="8">
-        <v>3500000</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10">
-        <v>3500000</v>
-      </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
-        <v>9493391</v>
-      </c>
-      <c r="B18" s="6">
-        <v>1071</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="8">
-        <v>11399338.199999999</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="9"/>
@@ -1384,17 +1380,89 @@
       <c r="K18" s="9"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10">
-        <v>11399338.199999999</v>
+        <v>4313807.5999999996</v>
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="10"/>
       <c r="Q18" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+        <v>4156674.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
+        <v>9493230</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1071</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="8">
+        <v>3500000</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10">
+        <v>3500000</v>
+      </c>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
+        <v>9493391</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1071</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="8">
+        <v>11399338.199999999</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10">
+        <v>11399338.199999999</v>
+      </c>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -574,10 +574,10 @@
         <v>150400857</v>
       </c>
       <c r="E2" s="8">
-        <v>13904760</v>
+        <v>14904760</v>
       </c>
       <c r="F2" s="8">
-        <v>0</v>
+        <v>2338980</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="9"/>
@@ -592,7 +592,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
-        <v>0</v>
+        <v>2338980</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -606,10 +606,10 @@
         <v>18</v>
       </c>
       <c r="D3" s="8">
-        <v>4000</v>
+        <v>59473.24</v>
       </c>
       <c r="E3" s="8">
-        <v>0</v>
+        <v>27311.19</v>
       </c>
       <c r="F3" s="8">
         <v>0</v>
@@ -621,7 +621,7 @@
       <c r="K3" s="9"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10">
-        <v>4000</v>
+        <v>59473.24</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -732,10 +732,10 @@
         <v>211141913.41999999</v>
       </c>
       <c r="E6" s="8">
-        <v>131342254.28</v>
+        <v>131794667.67</v>
       </c>
       <c r="F6" s="8">
-        <v>124923849.11</v>
+        <v>124935080.47</v>
       </c>
       <c r="G6" s="8">
         <v>15780164.470000001</v>
@@ -768,7 +768,7 @@
         <v>20635321.059999999</v>
       </c>
       <c r="Q6" s="10">
-        <v>145559170.16999999</v>
+        <v>145570401.53</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -947,7 +947,7 @@
         <v>199873.18</v>
       </c>
       <c r="F10" s="8">
-        <v>129204.08</v>
+        <v>155723.73000000001</v>
       </c>
       <c r="G10" s="8">
         <v>44810.879999999997</v>
@@ -980,7 +980,7 @@
         <v>39199.800000000003</v>
       </c>
       <c r="Q10" s="10">
-        <v>168403.88</v>
+        <v>194923.53</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -994,13 +994,13 @@
         <v>25</v>
       </c>
       <c r="D11" s="8">
-        <v>2949530.86</v>
+        <v>2949980.43</v>
       </c>
       <c r="E11" s="8">
-        <v>1716012.47</v>
+        <v>1719696.27</v>
       </c>
       <c r="F11" s="8">
-        <v>938095.41</v>
+        <v>1391355.75</v>
       </c>
       <c r="G11" s="8">
         <v>302674.08</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="10">
-        <v>2949530.86</v>
+        <v>2949980.43</v>
       </c>
       <c r="N11" s="9">
         <v>12856.3</v>
@@ -1033,7 +1033,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q11" s="10">
-        <v>1206715.47</v>
+        <v>1659975.81</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1106,7 +1106,7 @@
         <v>4009791.62</v>
       </c>
       <c r="F13" s="8">
-        <v>2539910.5</v>
+        <v>3384084.74</v>
       </c>
       <c r="G13" s="8">
         <v>565340.29</v>
@@ -1139,7 +1139,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q13" s="10">
-        <v>3016850.76</v>
+        <v>3861025</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1365,10 +1365,10 @@
         <v>23</v>
       </c>
       <c r="D18" s="8">
-        <v>4313807.5999999996</v>
+        <v>4313445.5999999996</v>
       </c>
       <c r="E18" s="8">
-        <v>4156674.7</v>
+        <v>4156312.7</v>
       </c>
       <c r="F18" s="8">
         <v>4156674.7</v>
@@ -1380,7 +1380,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10">
-        <v>4313807.5999999996</v>
+        <v>4313445.5999999996</v>
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -571,13 +571,13 @@
         <v>17</v>
       </c>
       <c r="D2" s="8">
-        <v>150400857</v>
+        <v>154400857</v>
       </c>
       <c r="E2" s="8">
         <v>14904760</v>
       </c>
       <c r="F2" s="8">
-        <v>2338980</v>
+        <v>14904760</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="9"/>
@@ -586,13 +586,13 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10">
-        <v>150400857</v>
+        <v>154400857</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
-        <v>2338980</v>
+        <v>14904760</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -609,10 +609,10 @@
         <v>59473.24</v>
       </c>
       <c r="E3" s="8">
-        <v>27311.19</v>
+        <v>55473.24</v>
       </c>
       <c r="F3" s="8">
-        <v>0</v>
+        <v>28162.05</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
@@ -627,7 +627,7 @@
       <c r="O3" s="9"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10">
-        <v>0</v>
+        <v>28162.05</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -729,13 +729,13 @@
         <v>21</v>
       </c>
       <c r="D6" s="8">
-        <v>211141913.41999999</v>
+        <v>211141912.72</v>
       </c>
       <c r="E6" s="8">
-        <v>131794667.67</v>
+        <v>133291644.48</v>
       </c>
       <c r="F6" s="8">
-        <v>124935080.47</v>
+        <v>125382064.92</v>
       </c>
       <c r="G6" s="8">
         <v>15780164.470000001</v>
@@ -756,7 +756,7 @@
         <v>10625717.609999999</v>
       </c>
       <c r="M6" s="10">
-        <v>200516195.81</v>
+        <v>200516195.11000001</v>
       </c>
       <c r="N6" s="9">
         <v>5029440.01</v>
@@ -768,7 +768,7 @@
         <v>20635321.059999999</v>
       </c>
       <c r="Q6" s="10">
-        <v>145570401.53</v>
+        <v>146017385.97999999</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -888,7 +888,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>216624.1</v>
+        <v>197943.42</v>
       </c>
       <c r="E9" s="8">
         <v>153457.43</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>216624.1</v>
+        <v>197943.42</v>
       </c>
       <c r="N9" s="9">
         <v>23722.79</v>
@@ -947,7 +947,7 @@
         <v>199873.18</v>
       </c>
       <c r="F10" s="8">
-        <v>155723.73000000001</v>
+        <v>156144.37</v>
       </c>
       <c r="G10" s="8">
         <v>44810.879999999997</v>
@@ -980,7 +980,7 @@
         <v>39199.800000000003</v>
       </c>
       <c r="Q10" s="10">
-        <v>194923.53</v>
+        <v>195344.17</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -994,13 +994,13 @@
         <v>25</v>
       </c>
       <c r="D11" s="8">
-        <v>2949980.43</v>
+        <v>2950140.91</v>
       </c>
       <c r="E11" s="8">
-        <v>1719696.27</v>
+        <v>1719856.75</v>
       </c>
       <c r="F11" s="8">
-        <v>1391355.75</v>
+        <v>1391516.23</v>
       </c>
       <c r="G11" s="8">
         <v>302674.08</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="10">
-        <v>2949980.43</v>
+        <v>2950140.91</v>
       </c>
       <c r="N11" s="9">
         <v>12856.3</v>
@@ -1033,7 +1033,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q11" s="10">
-        <v>1659975.81</v>
+        <v>1660136.29</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1053,7 +1053,7 @@
         <v>216550.42</v>
       </c>
       <c r="F12" s="8">
-        <v>141955.49</v>
+        <v>181711.6</v>
       </c>
       <c r="G12" s="8">
         <v>46987.59</v>
@@ -1086,7 +1086,7 @@
         <v>39709.360000000001</v>
       </c>
       <c r="Q12" s="10">
-        <v>181664.85</v>
+        <v>221420.96</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1162,7 +1162,7 @@
         <v>296909.12</v>
       </c>
       <c r="G14" s="8">
-        <v>419950.5</v>
+        <v>538633.05000000005</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1186,13 +1186,13 @@
         <v>0</v>
       </c>
       <c r="O14" s="9">
-        <v>405791.88</v>
+        <v>518777.67</v>
       </c>
       <c r="P14" s="10">
-        <v>405791.88</v>
+        <v>518777.67</v>
       </c>
       <c r="Q14" s="10">
-        <v>702701</v>
+        <v>815686.79</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1368,10 +1368,10 @@
         <v>4313445.5999999996</v>
       </c>
       <c r="E18" s="8">
-        <v>4156312.7</v>
+        <v>4156511</v>
       </c>
       <c r="F18" s="8">
-        <v>4156674.7</v>
+        <v>4156873</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="9"/>
@@ -1386,7 +1386,7 @@
       <c r="O18" s="9"/>
       <c r="P18" s="10"/>
       <c r="Q18" s="10">
-        <v>4156674.7</v>
+        <v>4156873</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
         <v>156450857</v>
       </c>
       <c r="E2" t="n">
-        <v>14904760</v>
+        <v>20954760</v>
       </c>
       <c r="F2" t="n">
         <v>14904760</v>
@@ -1082,10 +1082,10 @@
         <v>6014429.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4024851.67</v>
+        <v>4775388.7</v>
       </c>
       <c r="F13" t="n">
-        <v>3384084.74</v>
+        <v>3834653.59</v>
       </c>
       <c r="G13" t="n">
         <v>565340.29</v>
@@ -1118,7 +1118,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>3861025</v>
+        <v>4311593.85</v>
       </c>
     </row>
     <row r="14">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -920,7 +920,7 @@
         <v>199873.18</v>
       </c>
       <c r="F10" t="n">
-        <v>156144.37</v>
+        <v>168960.19</v>
       </c>
       <c r="G10" t="n">
         <v>44810.88</v>
@@ -953,7 +953,7 @@
         <v>39199.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>195344.17</v>
+        <v>208159.99</v>
       </c>
     </row>
     <row r="11">
@@ -1082,7 +1082,7 @@
         <v>6014429.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4775388.7</v>
+        <v>5448987.3</v>
       </c>
       <c r="F13" t="n">
         <v>3834653.59</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4313445.6</v>
+        <v>4359488.91</v>
       </c>
       <c r="E18" t="n">
         <v>4156511</v>
@@ -1369,7 +1369,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>4313445.6</v>
+        <v>4359488.91</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -972,10 +972,10 @@
         <v>2950140.91</v>
       </c>
       <c r="E11" t="n">
-        <v>1719856.75</v>
+        <v>1721869.15</v>
       </c>
       <c r="F11" t="n">
-        <v>1391516.23</v>
+        <v>1393528.63</v>
       </c>
       <c r="G11" t="n">
         <v>302674.08</v>
@@ -1008,7 +1008,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1660136.29</v>
+        <v>1662148.69</v>
       </c>
     </row>
     <row r="12">
@@ -1085,7 +1085,7 @@
         <v>5448987.3</v>
       </c>
       <c r="F13" t="n">
-        <v>3834653.59</v>
+        <v>4598817.12</v>
       </c>
       <c r="G13" t="n">
         <v>565340.29</v>
@@ -1118,7 +1118,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>4311593.85</v>
+        <v>5075757.38</v>
       </c>
     </row>
     <row r="14">
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4359488.91</v>
+        <v>4439049.16</v>
       </c>
       <c r="E18" t="n">
-        <v>4156511</v>
+        <v>4158780.8</v>
       </c>
       <c r="F18" t="n">
-        <v>4156873</v>
+        <v>4159142.8</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1369,13 +1369,13 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>4359488.91</v>
+        <v>4439049.16</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>4156873</v>
+        <v>4159142.8</v>
       </c>
     </row>
     <row r="19">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +534,7 @@
         <v>20954760</v>
       </c>
       <c r="F2" t="n">
-        <v>14904760</v>
+        <v>20954760</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -549,7 +549,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>14904760</v>
+        <v>20954760</v>
       </c>
     </row>
     <row r="3">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2950140.91</v>
+        <v>3080867.29</v>
       </c>
       <c r="E11" t="n">
-        <v>1721869.15</v>
+        <v>1723453.65</v>
       </c>
       <c r="F11" t="n">
-        <v>1393528.63</v>
+        <v>1395113.13</v>
       </c>
       <c r="G11" t="n">
         <v>302674.08</v>
@@ -987,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="M11" t="n">
-        <v>2950140.91</v>
+        <v>2354829.32</v>
       </c>
       <c r="N11" t="n">
         <v>12856.3</v>
@@ -1008,7 +1008,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>1662148.69</v>
+        <v>1663733.19</v>
       </c>
     </row>
     <row r="12">
@@ -1357,10 +1357,10 @@
         <v>4439049.16</v>
       </c>
       <c r="E18" t="n">
-        <v>4158780.8</v>
+        <v>4188380.8</v>
       </c>
       <c r="F18" t="n">
-        <v>4159142.8</v>
+        <v>4188742.8</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>4159142.8</v>
+        <v>4188742.8</v>
       </c>
     </row>
     <row r="19">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,10 +531,10 @@
         <v>156450857</v>
       </c>
       <c r="E2" t="n">
-        <v>20954760</v>
+        <v>35954760</v>
       </c>
       <c r="F2" t="n">
-        <v>20954760</v>
+        <v>35954760</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -549,7 +549,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>20954760</v>
+        <v>35954760</v>
       </c>
     </row>
     <row r="3">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59473.24</v>
+        <v>87830.81</v>
       </c>
       <c r="E3" t="n">
-        <v>55473.24</v>
+        <v>56199.99</v>
       </c>
       <c r="F3" t="n">
-        <v>28162.05</v>
+        <v>28888.8</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -580,13 +580,13 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>59473.24</v>
+        <v>87830.81</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>28162.05</v>
+        <v>28888.8</v>
       </c>
     </row>
     <row r="4">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>211141912.72</v>
+        <v>254377807.03</v>
       </c>
       <c r="E6" t="n">
-        <v>134784227.89</v>
+        <v>135023840.44</v>
       </c>
       <c r="F6" t="n">
         <v>128335750.43</v>
@@ -721,7 +721,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M6" t="n">
-        <v>200516195.11</v>
+        <v>243752089.42</v>
       </c>
       <c r="N6" t="n">
         <v>5029440.01</v>
@@ -738,18 +738,18 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9456627</v>
+        <v>9456622</v>
       </c>
       <c r="B7" t="n">
-        <v>1401</v>
+        <v>4251</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2400949</v>
+        <v>25150.45</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -757,63 +757,45 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
-        <v>172000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>2400949</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>169987.02</v>
-      </c>
-      <c r="P7" t="n">
-        <v>169987.02</v>
-      </c>
+        <v>25150.45</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>169987.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9468055</v>
+        <v>9456627</v>
       </c>
       <c r="B8" t="n">
-        <v>1221</v>
+        <v>1401</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>245207.82</v>
+        <v>2400949</v>
       </c>
       <c r="E8" t="n">
-        <v>156412.51</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>132217.76</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>31325.06</v>
+        <v>172000</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -822,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>9651.6</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>9651.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>235556.22</v>
+        <v>2400949</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26472.9</v>
+        <v>169987.02</v>
       </c>
       <c r="P8" t="n">
-        <v>26472.9</v>
+        <v>169987.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>158690.66</v>
+        <v>169987.02</v>
       </c>
     </row>
     <row r="9">
@@ -851,24 +833,24 @@
         <v>9468055</v>
       </c>
       <c r="B9" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>197943.42</v>
+        <v>261577.61</v>
       </c>
       <c r="E9" t="n">
-        <v>153457.43</v>
+        <v>201231.15</v>
       </c>
       <c r="F9" t="n">
-        <v>105979.8</v>
+        <v>170102.42</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>31325.06</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -877,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="M9" t="n">
-        <v>197943.42</v>
+        <v>251926.01</v>
       </c>
       <c r="N9" t="n">
-        <v>23722.79</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>26472.9</v>
       </c>
       <c r="P9" t="n">
-        <v>23722.79</v>
+        <v>26472.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>129702.59</v>
+        <v>196575.32</v>
       </c>
     </row>
     <row r="10">
@@ -906,24 +888,24 @@
         <v>9468055</v>
       </c>
       <c r="B10" t="n">
-        <v>1481</v>
+        <v>1231</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>292917.3</v>
+        <v>197943.42</v>
       </c>
       <c r="E10" t="n">
-        <v>199873.18</v>
+        <v>196632.42</v>
       </c>
       <c r="F10" t="n">
-        <v>168960.19</v>
+        <v>142480.5</v>
       </c>
       <c r="G10" t="n">
-        <v>44810.88</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -941,19 +923,19 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>292917.3</v>
+        <v>197943.42</v>
       </c>
       <c r="N10" t="n">
-        <v>1339.42</v>
+        <v>23722.79</v>
       </c>
       <c r="O10" t="n">
-        <v>37860.38</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>39199.8</v>
+        <v>23722.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>208159.99</v>
+        <v>166203.29</v>
       </c>
     </row>
     <row r="11">
@@ -961,24 +943,24 @@
         <v>9468055</v>
       </c>
       <c r="B11" t="n">
-        <v>1501</v>
+        <v>1481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3080867.29</v>
+        <v>292917.3</v>
       </c>
       <c r="E11" t="n">
-        <v>1723453.65</v>
+        <v>199873.18</v>
       </c>
       <c r="F11" t="n">
-        <v>1395113.13</v>
+        <v>168960.19</v>
       </c>
       <c r="G11" t="n">
-        <v>302674.08</v>
+        <v>44810.88</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -987,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2354829.32</v>
+        <v>292917.3</v>
       </c>
       <c r="N11" t="n">
-        <v>12856.3</v>
+        <v>1339.42</v>
       </c>
       <c r="O11" t="n">
-        <v>255763.76</v>
+        <v>37860.38</v>
       </c>
       <c r="P11" t="n">
-        <v>268620.06</v>
+        <v>39199.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1663733.19</v>
+        <v>208159.99</v>
       </c>
     </row>
     <row r="12">
@@ -1016,24 +998,24 @@
         <v>9468055</v>
       </c>
       <c r="B12" t="n">
-        <v>4251</v>
+        <v>1501</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>304289.25</v>
+        <v>3482120.78</v>
       </c>
       <c r="E12" t="n">
-        <v>216550.42</v>
+        <v>2244817.59</v>
       </c>
       <c r="F12" t="n">
-        <v>181711.6</v>
+        <v>1457193.98</v>
       </c>
       <c r="G12" t="n">
-        <v>46987.59</v>
+        <v>302674.08</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1042,53 +1024,53 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="M12" t="n">
-        <v>304289.25</v>
+        <v>2756082.81</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>12856.3</v>
       </c>
       <c r="O12" t="n">
-        <v>39709.36</v>
+        <v>255763.76</v>
       </c>
       <c r="P12" t="n">
-        <v>39709.36</v>
+        <v>268620.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>221420.96</v>
+        <v>1725814.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9468057</v>
+        <v>9468055</v>
       </c>
       <c r="B13" t="n">
-        <v>1371</v>
+        <v>4251</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6014429.4</v>
+        <v>304289.25</v>
       </c>
       <c r="E13" t="n">
-        <v>5448987.3</v>
+        <v>216550.42</v>
       </c>
       <c r="F13" t="n">
-        <v>4598817.12</v>
+        <v>181711.6</v>
       </c>
       <c r="G13" t="n">
-        <v>565340.29</v>
+        <v>46987.59</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1106,44 +1088,44 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>6014429.4</v>
+        <v>304289.25</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="P13" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>5075757.38</v>
+        <v>221420.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9470658</v>
+        <v>9468057</v>
       </c>
       <c r="B14" t="n">
-        <v>1231</v>
+        <v>1371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2592199.31</v>
+        <v>6014429.4</v>
       </c>
       <c r="E14" t="n">
-        <v>296909.12</v>
+        <v>5448987.3</v>
       </c>
       <c r="F14" t="n">
-        <v>296909.12</v>
+        <v>4598817.12</v>
       </c>
       <c r="G14" t="n">
-        <v>538633.05</v>
+        <v>565340.29</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1152,53 +1134,53 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>35398.54</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>35398.54</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2556800.77</v>
+        <v>6014429.4</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>518777.67</v>
+        <v>476940.26</v>
       </c>
       <c r="P14" t="n">
-        <v>518777.67</v>
+        <v>476940.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>815686.79</v>
+        <v>5075757.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9473170</v>
+        <v>9470658</v>
       </c>
       <c r="B15" t="n">
-        <v>2301</v>
+        <v>1231</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>736365.61</v>
+        <v>2592199.31</v>
       </c>
       <c r="E15" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="F15" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="G15" t="n">
-        <v>188341.65</v>
+        <v>538633.05</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1207,53 +1189,53 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>197622.57</v>
+        <v>35398.54</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>197622.57</v>
+        <v>35398.54</v>
       </c>
       <c r="M15" t="n">
-        <v>538743.04</v>
+        <v>2556800.77</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>188341.65</v>
+        <v>518777.67</v>
       </c>
       <c r="P15" t="n">
-        <v>188341.65</v>
+        <v>518777.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>538743.04</v>
+        <v>815686.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9473171</v>
+        <v>9473170</v>
       </c>
       <c r="B16" t="n">
-        <v>1221</v>
+        <v>2301</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11555415.79</v>
+        <v>736365.61</v>
       </c>
       <c r="E16" t="n">
-        <v>58086.92</v>
+        <v>350401.39</v>
       </c>
       <c r="F16" t="n">
-        <v>58086.92</v>
+        <v>350401.39</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1262,53 +1244,53 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="M16" t="n">
-        <v>11555415.79</v>
+        <v>538743.04</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>58086.92</v>
+        <v>538743.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9474703</v>
+        <v>9473171</v>
       </c>
       <c r="B17" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79058892.34999999</v>
+        <v>11555415.79</v>
       </c>
       <c r="E17" t="n">
-        <v>78541892.26000001</v>
+        <v>58086.92</v>
       </c>
       <c r="F17" t="n">
-        <v>77547634.67</v>
+        <v>58086.92</v>
       </c>
       <c r="G17" t="n">
-        <v>517000</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1326,78 +1308,96 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>79058892.34999999</v>
+        <v>11555415.79</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>509950</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>509950</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>78057584.67</v>
+        <v>58086.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9480259</v>
+        <v>9474703</v>
       </c>
       <c r="B18" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4439049.16</v>
+        <v>79058892.34999999</v>
       </c>
       <c r="E18" t="n">
-        <v>4188380.8</v>
+        <v>78541892.26000001</v>
       </c>
       <c r="F18" t="n">
-        <v>4188742.8</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+        <v>77547634.67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>517000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="n">
-        <v>4439049.16</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>79058892.34999999</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>509950</v>
+      </c>
+      <c r="P18" t="n">
+        <v>509950</v>
+      </c>
       <c r="Q18" t="n">
-        <v>4188742.8</v>
+        <v>78057584.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9493230</v>
+        <v>9480259</v>
       </c>
       <c r="B19" t="n">
-        <v>1071</v>
+        <v>1221</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3500000</v>
+        <v>4439049.16</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>4249063.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4249425.4</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1406,18 +1406,18 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>3500000</v>
+        <v>4439049.16</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4249425.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9493391</v>
+        <v>9493230</v>
       </c>
       <c r="B20" t="n">
         <v>1071</v>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1443,7 +1443,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1452,6 +1452,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9493391</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1071</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11399338.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>11399338.2</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,10 +568,10 @@
         <v>87830.81</v>
       </c>
       <c r="E3" t="n">
-        <v>56199.99</v>
+        <v>85269.56</v>
       </c>
       <c r="F3" t="n">
-        <v>28888.8</v>
+        <v>30092.6</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -586,7 +586,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>28888.8</v>
+        <v>30092.6</v>
       </c>
     </row>
     <row r="4">
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>254377807.03</v>
+        <v>317627575.8</v>
       </c>
       <c r="E6" t="n">
-        <v>135023840.44</v>
+        <v>139476442.75</v>
       </c>
       <c r="F6" t="n">
-        <v>128335750.43</v>
+        <v>129519436.45</v>
       </c>
       <c r="G6" t="n">
         <v>15780164.47</v>
@@ -721,7 +721,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M6" t="n">
-        <v>243752089.42</v>
+        <v>307001858.19</v>
       </c>
       <c r="N6" t="n">
         <v>5029440.01</v>
@@ -733,7 +733,7 @@
         <v>20635321.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>148971071.49</v>
+        <v>150154757.51</v>
       </c>
     </row>
     <row r="7">
@@ -752,7 +752,7 @@
         <v>25150.45</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>12923.76</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -830,57 +830,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9468055</v>
+        <v>9456627</v>
       </c>
       <c r="B9" t="n">
-        <v>1221</v>
+        <v>1511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>261577.61</v>
+        <v>121487.74</v>
       </c>
       <c r="E9" t="n">
-        <v>201231.15</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>170102.42</v>
-      </c>
-      <c r="G9" t="n">
-        <v>31325.06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9651.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9651.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>251926.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>26472.9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>26472.9</v>
-      </c>
+        <v>121487.74</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>196575.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -888,24 +870,24 @@
         <v>9468055</v>
       </c>
       <c r="B10" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>197943.42</v>
+        <v>261577.61</v>
       </c>
       <c r="E10" t="n">
-        <v>196632.42</v>
+        <v>201231.15</v>
       </c>
       <c r="F10" t="n">
-        <v>142480.5</v>
+        <v>170102.42</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>31325.06</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -914,28 +896,28 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="M10" t="n">
-        <v>197943.42</v>
+        <v>251926.01</v>
       </c>
       <c r="N10" t="n">
-        <v>23722.79</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>26472.9</v>
       </c>
       <c r="P10" t="n">
-        <v>23722.79</v>
+        <v>26472.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>166203.29</v>
+        <v>196575.32</v>
       </c>
     </row>
     <row r="11">
@@ -943,24 +925,24 @@
         <v>9468055</v>
       </c>
       <c r="B11" t="n">
-        <v>1481</v>
+        <v>1231</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>292917.3</v>
+        <v>197943.42</v>
       </c>
       <c r="E11" t="n">
-        <v>199873.18</v>
+        <v>196632.42</v>
       </c>
       <c r="F11" t="n">
-        <v>168960.19</v>
+        <v>142480.5</v>
       </c>
       <c r="G11" t="n">
-        <v>44810.88</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -978,19 +960,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>292917.3</v>
+        <v>197943.42</v>
       </c>
       <c r="N11" t="n">
-        <v>1339.42</v>
+        <v>23722.79</v>
       </c>
       <c r="O11" t="n">
-        <v>37860.38</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>39199.8</v>
+        <v>23722.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>208159.99</v>
+        <v>166203.29</v>
       </c>
     </row>
     <row r="12">
@@ -998,24 +980,24 @@
         <v>9468055</v>
       </c>
       <c r="B12" t="n">
-        <v>1501</v>
+        <v>1481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3482120.78</v>
+        <v>357832.97</v>
       </c>
       <c r="E12" t="n">
-        <v>2244817.59</v>
+        <v>268716.71</v>
       </c>
       <c r="F12" t="n">
-        <v>1457193.98</v>
+        <v>168960.19</v>
       </c>
       <c r="G12" t="n">
-        <v>302674.08</v>
+        <v>44810.88</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1024,28 +1006,28 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2756082.81</v>
+        <v>357832.97</v>
       </c>
       <c r="N12" t="n">
-        <v>12856.3</v>
+        <v>1339.42</v>
       </c>
       <c r="O12" t="n">
-        <v>255763.76</v>
+        <v>37860.38</v>
       </c>
       <c r="P12" t="n">
-        <v>268620.06</v>
+        <v>39199.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1725814.04</v>
+        <v>208159.99</v>
       </c>
     </row>
     <row r="13">
@@ -1053,24 +1035,24 @@
         <v>9468055</v>
       </c>
       <c r="B13" t="n">
-        <v>4251</v>
+        <v>1501</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>304289.25</v>
+        <v>3482519.1</v>
       </c>
       <c r="E13" t="n">
-        <v>216550.42</v>
+        <v>2245353.71</v>
       </c>
       <c r="F13" t="n">
-        <v>181711.6</v>
+        <v>1830986.97</v>
       </c>
       <c r="G13" t="n">
-        <v>46987.59</v>
+        <v>302674.08</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1079,53 +1061,53 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="M13" t="n">
-        <v>304289.25</v>
+        <v>2756481.13</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>12856.3</v>
       </c>
       <c r="O13" t="n">
-        <v>39709.36</v>
+        <v>255763.76</v>
       </c>
       <c r="P13" t="n">
-        <v>39709.36</v>
+        <v>268620.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>221420.96</v>
+        <v>2099607.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9468057</v>
+        <v>9468055</v>
       </c>
       <c r="B14" t="n">
-        <v>1371</v>
+        <v>4251</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6014429.4</v>
+        <v>369149.3</v>
       </c>
       <c r="E14" t="n">
-        <v>5448987.3</v>
+        <v>265355.88</v>
       </c>
       <c r="F14" t="n">
-        <v>4598817.12</v>
+        <v>181711.6</v>
       </c>
       <c r="G14" t="n">
-        <v>565340.29</v>
+        <v>46987.59</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1143,44 +1125,44 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6014429.4</v>
+        <v>369149.3</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="P14" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>5075757.38</v>
+        <v>221420.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9470658</v>
+        <v>9468057</v>
       </c>
       <c r="B15" t="n">
-        <v>1231</v>
+        <v>1371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2592199.31</v>
+        <v>7110843.9</v>
       </c>
       <c r="E15" t="n">
-        <v>296909.12</v>
+        <v>5448987.3</v>
       </c>
       <c r="F15" t="n">
-        <v>296909.12</v>
+        <v>4598817.12</v>
       </c>
       <c r="G15" t="n">
-        <v>538633.05</v>
+        <v>565340.29</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1189,53 +1171,53 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>35398.54</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>35398.54</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2556800.77</v>
+        <v>7110843.9</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>518777.67</v>
+        <v>476940.26</v>
       </c>
       <c r="P15" t="n">
-        <v>518777.67</v>
+        <v>476940.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>815686.79</v>
+        <v>5075757.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9473170</v>
+        <v>9470658</v>
       </c>
       <c r="B16" t="n">
-        <v>2301</v>
+        <v>1231</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>736365.61</v>
+        <v>2592199.31</v>
       </c>
       <c r="E16" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="F16" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="G16" t="n">
-        <v>188341.65</v>
+        <v>538633.05</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1244,53 +1226,53 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>197622.57</v>
+        <v>35398.54</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>197622.57</v>
+        <v>35398.54</v>
       </c>
       <c r="M16" t="n">
-        <v>538743.04</v>
+        <v>2556800.77</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>188341.65</v>
+        <v>518777.67</v>
       </c>
       <c r="P16" t="n">
-        <v>188341.65</v>
+        <v>518777.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>538743.04</v>
+        <v>815686.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9473171</v>
+        <v>9473170</v>
       </c>
       <c r="B17" t="n">
-        <v>1221</v>
+        <v>2301</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11555415.79</v>
+        <v>736365.61</v>
       </c>
       <c r="E17" t="n">
-        <v>58086.92</v>
+        <v>350401.39</v>
       </c>
       <c r="F17" t="n">
-        <v>58086.92</v>
+        <v>350401.39</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1299,53 +1281,53 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="M17" t="n">
-        <v>11555415.79</v>
+        <v>538743.04</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>58086.92</v>
+        <v>538743.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9474703</v>
+        <v>9473171</v>
       </c>
       <c r="B18" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>79058892.34999999</v>
+        <v>13190931.14</v>
       </c>
       <c r="E18" t="n">
-        <v>78541892.26000001</v>
+        <v>117990.78</v>
       </c>
       <c r="F18" t="n">
-        <v>77547634.67</v>
+        <v>117990.78</v>
       </c>
       <c r="G18" t="n">
-        <v>517000</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1363,78 +1345,96 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>79058892.34999999</v>
+        <v>13190931.14</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>509950</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>509950</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78057584.67</v>
+        <v>117990.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9480259</v>
+        <v>9474703</v>
       </c>
       <c r="B19" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4439049.16</v>
+        <v>79058892.34999999</v>
       </c>
       <c r="E19" t="n">
-        <v>4249063.4</v>
+        <v>78541892.26000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4249425.4</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+        <v>77547634.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>517000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="n">
-        <v>4439049.16</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+        <v>79058892.34999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>509950</v>
+      </c>
+      <c r="P19" t="n">
+        <v>509950</v>
+      </c>
       <c r="Q19" t="n">
-        <v>4249425.4</v>
+        <v>78057584.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9493230</v>
+        <v>9480259</v>
       </c>
       <c r="B20" t="n">
-        <v>1071</v>
+        <v>1221</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3500000</v>
+        <v>4439049.16</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4277969.53</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4278331.53</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1443,18 +1443,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>3500000</v>
+        <v>4439049.16</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4278331.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9493391</v>
+        <v>9493230</v>
       </c>
       <c r="B21" t="n">
         <v>1071</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1480,7 +1480,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1489,6 +1489,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9493391</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1071</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11399338.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>11399338.2</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9501917</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1491</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -531,10 +531,10 @@
         <v>156450857</v>
       </c>
       <c r="E2" t="n">
-        <v>35954760</v>
+        <v>70206661.34</v>
       </c>
       <c r="F2" t="n">
-        <v>35954760</v>
+        <v>51394844.34</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -549,7 +549,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>35954760</v>
+        <v>51394844.34</v>
       </c>
     </row>
     <row r="3">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>87830.81</v>
+        <v>947695.28</v>
       </c>
       <c r="E3" t="n">
-        <v>85269.56</v>
+        <v>945624.83</v>
       </c>
       <c r="F3" t="n">
         <v>30092.6</v>
@@ -580,7 +580,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>87830.81</v>
+        <v>947695.28</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>317627575.8</v>
+        <v>327537649.47</v>
       </c>
       <c r="E6" t="n">
-        <v>139476442.75</v>
+        <v>141482165.2</v>
       </c>
       <c r="F6" t="n">
-        <v>129519436.45</v>
+        <v>131458449.45</v>
       </c>
       <c r="G6" t="n">
         <v>15780164.47</v>
@@ -721,7 +721,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M6" t="n">
-        <v>307001858.19</v>
+        <v>316911931.86</v>
       </c>
       <c r="N6" t="n">
         <v>5029440.01</v>
@@ -733,7 +733,7 @@
         <v>20635321.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>150154757.51</v>
+        <v>152093770.51</v>
       </c>
     </row>
     <row r="7">
@@ -752,7 +752,7 @@
         <v>25150.45</v>
       </c>
       <c r="E7" t="n">
-        <v>12923.76</v>
+        <v>13676.35</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>121487.74</v>
+        <v>188000.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>121487.74</v>
+        <v>188000.6</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>197943.42</v>
+        <v>199474.66</v>
       </c>
       <c r="E11" t="n">
         <v>196632.42</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>197943.42</v>
+        <v>199474.66</v>
       </c>
       <c r="N11" t="n">
         <v>23722.79</v>
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>357832.97</v>
+        <v>410943.68</v>
       </c>
       <c r="E12" t="n">
-        <v>268716.71</v>
+        <v>268838</v>
       </c>
       <c r="F12" t="n">
-        <v>168960.19</v>
+        <v>227269.37</v>
       </c>
       <c r="G12" t="n">
         <v>44810.88</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>357832.97</v>
+        <v>410943.68</v>
       </c>
       <c r="N12" t="n">
         <v>1339.42</v>
@@ -1027,7 +1027,7 @@
         <v>39199.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>208159.99</v>
+        <v>266469.17</v>
       </c>
     </row>
     <row r="13">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3482519.1</v>
+        <v>3509819.1</v>
       </c>
       <c r="E13" t="n">
-        <v>2245353.71</v>
+        <v>2245817.21</v>
       </c>
       <c r="F13" t="n">
-        <v>1830986.97</v>
+        <v>1675043.36</v>
       </c>
       <c r="G13" t="n">
         <v>302674.08</v>
@@ -1070,7 +1070,7 @@
         <v>726037.97</v>
       </c>
       <c r="M13" t="n">
-        <v>2756481.13</v>
+        <v>2783781.13</v>
       </c>
       <c r="N13" t="n">
         <v>12856.3</v>
@@ -1082,7 +1082,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>2099607.03</v>
+        <v>1943663.42</v>
       </c>
     </row>
     <row r="14">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>369149.3</v>
+        <v>422138.72</v>
       </c>
       <c r="E14" t="n">
-        <v>265355.88</v>
+        <v>281725.67</v>
       </c>
       <c r="F14" t="n">
-        <v>181711.6</v>
+        <v>236804.79</v>
       </c>
       <c r="G14" t="n">
         <v>46987.59</v>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>369149.3</v>
+        <v>422138.72</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>39709.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>221420.96</v>
+        <v>276514.15</v>
       </c>
     </row>
     <row r="15">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7110843.9</v>
+        <v>7172880.18</v>
       </c>
       <c r="E15" t="n">
-        <v>5448987.3</v>
+        <v>5620576.29</v>
       </c>
       <c r="F15" t="n">
         <v>4598817.12</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7110843.9</v>
+        <v>7172880.18</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13190931.14</v>
+        <v>14727208.7</v>
       </c>
       <c r="E18" t="n">
-        <v>117990.78</v>
+        <v>3358783.69</v>
       </c>
       <c r="F18" t="n">
-        <v>117990.78</v>
+        <v>3289783.69</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>13190931.14</v>
+        <v>14727208.7</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>117990.78</v>
+        <v>3289783.69</v>
       </c>
     </row>
     <row r="19">
@@ -1545,7 +1545,7 @@
         <v>7500000</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3750000</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3750000</v>
       </c>
     </row>
   </sheetData>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,10 +531,10 @@
         <v>156450857</v>
       </c>
       <c r="E2" t="n">
-        <v>70206661.34</v>
+        <v>70847450.34</v>
       </c>
       <c r="F2" t="n">
-        <v>51394844.34</v>
+        <v>70847450.34</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -549,7 +549,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>51394844.34</v>
+        <v>70847450.34</v>
       </c>
     </row>
     <row r="3">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>947695.28</v>
+        <v>5973853.61</v>
       </c>
       <c r="E3" t="n">
-        <v>945624.83</v>
+        <v>5943523.17</v>
       </c>
       <c r="F3" t="n">
-        <v>30092.6</v>
+        <v>5443034.08</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -580,13 +580,13 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>947695.28</v>
+        <v>5973853.61</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>30092.6</v>
+        <v>5443034.08</v>
       </c>
     </row>
     <row r="4">
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>327537649.47</v>
+        <v>331548615.17</v>
       </c>
       <c r="E6" t="n">
-        <v>141482165.2</v>
+        <v>141755234.7</v>
       </c>
       <c r="F6" t="n">
-        <v>131458449.45</v>
+        <v>134930268.69</v>
       </c>
       <c r="G6" t="n">
         <v>15780164.47</v>
@@ -721,7 +721,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M6" t="n">
-        <v>316911931.86</v>
+        <v>320922897.56</v>
       </c>
       <c r="N6" t="n">
         <v>5029440.01</v>
@@ -733,7 +733,7 @@
         <v>20635321.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>152093770.51</v>
+        <v>155565589.75</v>
       </c>
     </row>
     <row r="7">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25150.45</v>
+        <v>26623.94</v>
       </c>
       <c r="E7" t="n">
         <v>13676.35</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>13148.52</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -764,13 +764,13 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>25150.45</v>
+        <v>26623.94</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>13148.52</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>261577.61</v>
+        <v>298061.56</v>
       </c>
       <c r="E10" t="n">
         <v>201231.15</v>
@@ -905,7 +905,7 @@
         <v>9651.6</v>
       </c>
       <c r="M10" t="n">
-        <v>251926.01</v>
+        <v>288409.96</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>199474.66</v>
+        <v>264953.82</v>
       </c>
       <c r="E11" t="n">
         <v>196632.42</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>199474.66</v>
+        <v>264953.82</v>
       </c>
       <c r="N11" t="n">
         <v>23722.79</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3509819.1</v>
+        <v>3969459.37</v>
       </c>
       <c r="E13" t="n">
-        <v>2245817.21</v>
+        <v>2264376.08</v>
       </c>
       <c r="F13" t="n">
-        <v>1675043.36</v>
+        <v>1917121.77</v>
       </c>
       <c r="G13" t="n">
         <v>302674.08</v>
@@ -1070,7 +1070,7 @@
         <v>726037.97</v>
       </c>
       <c r="M13" t="n">
-        <v>2783781.13</v>
+        <v>3243421.4</v>
       </c>
       <c r="N13" t="n">
         <v>12856.3</v>
@@ -1082,7 +1082,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1943663.42</v>
+        <v>2185741.83</v>
       </c>
     </row>
     <row r="14">
@@ -1156,7 +1156,7 @@
         <v>7172880.18</v>
       </c>
       <c r="E15" t="n">
-        <v>5620576.29</v>
+        <v>6607411.69</v>
       </c>
       <c r="F15" t="n">
         <v>4598817.12</v>
@@ -1318,13 +1318,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14727208.7</v>
+        <v>14784813.95</v>
       </c>
       <c r="E18" t="n">
-        <v>3358783.69</v>
+        <v>3496783.69</v>
       </c>
       <c r="F18" t="n">
-        <v>3289783.69</v>
+        <v>3357748.69</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>14727208.7</v>
+        <v>14784813.95</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3289783.69</v>
+        <v>3357748.69</v>
       </c>
     </row>
     <row r="19">
@@ -1391,16 +1391,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M19" t="n">
-        <v>79058892.34999999</v>
+        <v>79058892.26000001</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4439049.16</v>
+        <v>8516020.279999999</v>
       </c>
       <c r="E20" t="n">
-        <v>4277969.53</v>
+        <v>8405155.640000001</v>
       </c>
       <c r="F20" t="n">
-        <v>4278331.53</v>
+        <v>8405517.640000001</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>4439049.16</v>
+        <v>8516020.279999999</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>4278331.53</v>
+        <v>8405517.640000001</v>
       </c>
     </row>
     <row r="21">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>331548615.17</v>
+        <v>331548538.62</v>
       </c>
       <c r="E6" t="n">
         <v>141755234.7</v>
       </c>
       <c r="F6" t="n">
-        <v>134930268.69</v>
+        <v>135209487.29</v>
       </c>
       <c r="G6" t="n">
         <v>15780164.47</v>
@@ -721,7 +721,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M6" t="n">
-        <v>320922897.56</v>
+        <v>320922821.01</v>
       </c>
       <c r="N6" t="n">
         <v>5029440.01</v>
@@ -733,7 +733,7 @@
         <v>20635321.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>155565589.75</v>
+        <v>155844808.35</v>
       </c>
     </row>
     <row r="7">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26623.94</v>
+        <v>37656.38</v>
       </c>
       <c r="E7" t="n">
-        <v>13676.35</v>
+        <v>25150.45</v>
       </c>
       <c r="F7" t="n">
         <v>13148.52</v>
@@ -764,7 +764,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>26623.94</v>
+        <v>37656.38</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>188000.6</v>
+        <v>195200.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>188000.6</v>
+        <v>195200.6</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -881,10 +881,10 @@
         <v>298061.56</v>
       </c>
       <c r="E10" t="n">
-        <v>201231.15</v>
+        <v>237715.09</v>
       </c>
       <c r="F10" t="n">
-        <v>170102.42</v>
+        <v>201064.33</v>
       </c>
       <c r="G10" t="n">
         <v>31325.06</v>
@@ -917,7 +917,7 @@
         <v>26472.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>196575.32</v>
+        <v>227537.23</v>
       </c>
     </row>
     <row r="11">
@@ -936,10 +936,10 @@
         <v>264953.82</v>
       </c>
       <c r="E11" t="n">
-        <v>196632.42</v>
+        <v>231894.37</v>
       </c>
       <c r="F11" t="n">
-        <v>142480.5</v>
+        <v>172455.6</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>23722.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>166203.29</v>
+        <v>196178.39</v>
       </c>
     </row>
     <row r="12">
@@ -991,7 +991,7 @@
         <v>410943.68</v>
       </c>
       <c r="E12" t="n">
-        <v>268838</v>
+        <v>321827.42</v>
       </c>
       <c r="F12" t="n">
         <v>227269.37</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3969459.37</v>
+        <v>3974459.37</v>
       </c>
       <c r="E13" t="n">
-        <v>2264376.08</v>
+        <v>2704618.85</v>
       </c>
       <c r="F13" t="n">
         <v>1917121.77</v>
@@ -1070,7 +1070,7 @@
         <v>726037.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3243421.4</v>
+        <v>3248421.4</v>
       </c>
       <c r="N13" t="n">
         <v>12856.3</v>
@@ -1101,7 +1101,7 @@
         <v>422138.72</v>
       </c>
       <c r="E14" t="n">
-        <v>281725.67</v>
+        <v>334715.09</v>
       </c>
       <c r="F14" t="n">
         <v>236804.79</v>
@@ -1159,7 +1159,7 @@
         <v>6607411.69</v>
       </c>
       <c r="F15" t="n">
-        <v>4598817.12</v>
+        <v>5579292.92</v>
       </c>
       <c r="G15" t="n">
         <v>565340.29</v>
@@ -1192,7 +1192,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>5075757.38</v>
+        <v>6056233.18</v>
       </c>
     </row>
     <row r="16">
@@ -1321,10 +1321,10 @@
         <v>14784813.95</v>
       </c>
       <c r="E18" t="n">
-        <v>3496783.69</v>
+        <v>3554388.94</v>
       </c>
       <c r="F18" t="n">
-        <v>3357748.69</v>
+        <v>3551283.94</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3357748.69</v>
+        <v>3551283.94</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         <v>8516020.279999999</v>
       </c>
       <c r="E20" t="n">
-        <v>8405155.640000001</v>
+        <v>8435171.699999999</v>
       </c>
       <c r="F20" t="n">
-        <v>8405517.640000001</v>
+        <v>8435533.699999999</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>8405517.640000001</v>
+        <v>8435533.699999999</v>
       </c>
     </row>
     <row r="21">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -568,10 +568,10 @@
         <v>5973853.61</v>
       </c>
       <c r="E3" t="n">
-        <v>5943523.17</v>
+        <v>5971783.16</v>
       </c>
       <c r="F3" t="n">
-        <v>5443034.08</v>
+        <v>5443523.17</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -586,7 +586,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>5443034.08</v>
+        <v>5443523.17</v>
       </c>
     </row>
     <row r="4">
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>331548538.62</v>
+        <v>330080538.62</v>
       </c>
       <c r="E6" t="n">
-        <v>141755234.7</v>
+        <v>143853637.96</v>
       </c>
       <c r="F6" t="n">
-        <v>135209487.29</v>
+        <v>135223103.73</v>
       </c>
       <c r="G6" t="n">
         <v>15780164.47</v>
@@ -721,7 +721,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M6" t="n">
-        <v>320922821.01</v>
+        <v>319454821.01</v>
       </c>
       <c r="N6" t="n">
         <v>5029440.01</v>
@@ -733,7 +733,7 @@
         <v>20635321.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>155844808.35</v>
+        <v>155858424.79</v>
       </c>
     </row>
     <row r="7">
@@ -752,10 +752,10 @@
         <v>37656.38</v>
       </c>
       <c r="E7" t="n">
-        <v>25150.45</v>
+        <v>37656.38</v>
       </c>
       <c r="F7" t="n">
-        <v>13148.52</v>
+        <v>13676.35</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -770,7 +770,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>13148.52</v>
+        <v>13676.35</v>
       </c>
     </row>
     <row r="8">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>195200.6</v>
+        <v>243900.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>195200.6</v>
+        <v>243900.6</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -994,7 +994,7 @@
         <v>321827.42</v>
       </c>
       <c r="F12" t="n">
-        <v>227269.37</v>
+        <v>272313.27</v>
       </c>
       <c r="G12" t="n">
         <v>44810.88</v>
@@ -1027,7 +1027,7 @@
         <v>39199.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>266469.17</v>
+        <v>311513.07</v>
       </c>
     </row>
     <row r="13">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3974459.37</v>
+        <v>3974538.91</v>
       </c>
       <c r="E13" t="n">
-        <v>2704618.85</v>
+        <v>2705821.89</v>
       </c>
       <c r="F13" t="n">
-        <v>1917121.77</v>
+        <v>1918324.81</v>
       </c>
       <c r="G13" t="n">
         <v>302674.08</v>
@@ -1070,7 +1070,7 @@
         <v>726037.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3248421.4</v>
+        <v>3248500.94</v>
       </c>
       <c r="N13" t="n">
         <v>12856.3</v>
@@ -1082,7 +1082,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>2185741.83</v>
+        <v>2186944.87</v>
       </c>
     </row>
     <row r="14">
@@ -1104,7 +1104,7 @@
         <v>334715.09</v>
       </c>
       <c r="F14" t="n">
-        <v>236804.79</v>
+        <v>281848.69</v>
       </c>
       <c r="G14" t="n">
         <v>46987.59</v>
@@ -1137,7 +1137,7 @@
         <v>39709.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>276514.15</v>
+        <v>321558.05</v>
       </c>
     </row>
     <row r="15">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7172880.18</v>
+        <v>7216216.2</v>
       </c>
       <c r="E15" t="n">
         <v>6607411.69</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7172880.18</v>
+        <v>7216216.2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>296909.12</v>
       </c>
       <c r="G16" t="n">
-        <v>538633.05</v>
+        <v>572010.63</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>518777.67</v>
+        <v>552155.25</v>
       </c>
       <c r="P16" t="n">
-        <v>518777.67</v>
+        <v>552155.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>815686.79</v>
+        <v>849064.37</v>
       </c>
     </row>
     <row r="17">
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8516020.279999999</v>
+        <v>8534591.699999999</v>
       </c>
       <c r="E20" t="n">
-        <v>8435171.699999999</v>
+        <v>8436908.5</v>
       </c>
       <c r="F20" t="n">
-        <v>8435533.699999999</v>
+        <v>8437270.5</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>8516020.279999999</v>
+        <v>8534591.699999999</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>8435533.699999999</v>
+        <v>8437270.5</v>
       </c>
     </row>
     <row r="21">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9445718</v>
+        <v>9445684</v>
       </c>
       <c r="B3" t="n">
         <v>4251</v>
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5973853.61</v>
+        <v>209101.99</v>
       </c>
       <c r="E3" t="n">
-        <v>5971783.16</v>
+        <v>209101.99</v>
       </c>
       <c r="F3" t="n">
-        <v>5443523.17</v>
+        <v>133252.22</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -580,35 +580,35 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>5973853.61</v>
+        <v>209101.99</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>5443523.17</v>
+        <v>133252.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9445721</v>
+        <v>9445718</v>
       </c>
       <c r="B4" t="n">
-        <v>1231</v>
+        <v>4251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9350820</v>
+        <v>5973853.61</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5971783.16</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5443523.17</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -617,68 +617,50 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>9350820</v>
+        <v>5973853.61</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5443523.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9452379</v>
+        <v>9445721</v>
       </c>
       <c r="B5" t="n">
-        <v>1491</v>
+        <v>1231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5000000</v>
+        <v>9350820</v>
       </c>
       <c r="E5" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2500000</v>
-      </c>
+        <v>9350820</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>2500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -686,24 +668,24 @@
         <v>9452379</v>
       </c>
       <c r="B6" t="n">
-        <v>2301</v>
+        <v>1491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>330080538.62</v>
+        <v>5000000</v>
       </c>
       <c r="E6" t="n">
-        <v>143853637.96</v>
+        <v>5000000</v>
       </c>
       <c r="F6" t="n">
-        <v>135223103.73</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>15780164.47</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -712,120 +694,120 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10601950.53</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>23767.08</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10625717.61</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>319454821.01</v>
+        <v>5000000</v>
       </c>
       <c r="N6" t="n">
-        <v>5029440.01</v>
+        <v>2500000</v>
       </c>
       <c r="O6" t="n">
-        <v>15605881.05</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>20635321.06</v>
+        <v>2500000</v>
       </c>
       <c r="Q6" t="n">
-        <v>155858424.79</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9456622</v>
+        <v>9452379</v>
       </c>
       <c r="B7" t="n">
-        <v>4251</v>
+        <v>2301</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37656.38</v>
+        <v>328550512.49</v>
       </c>
       <c r="E7" t="n">
-        <v>37656.38</v>
+        <v>145099795.85</v>
       </c>
       <c r="F7" t="n">
-        <v>13676.35</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>135223103.73</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17110597.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10601950.53</v>
+      </c>
+      <c r="K7" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10625717.61</v>
+      </c>
       <c r="M7" t="n">
-        <v>37656.38</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+        <v>317924794.88</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5029440.01</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15605881.05</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20635321.06</v>
+      </c>
       <c r="Q7" t="n">
-        <v>13676.35</v>
+        <v>155858424.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9456627</v>
+        <v>9456622</v>
       </c>
       <c r="B8" t="n">
-        <v>1401</v>
+        <v>4251</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2400949</v>
+        <v>37656.38</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>37656.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>172000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+        <v>13676.35</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>2400949</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>169987.02</v>
-      </c>
-      <c r="P8" t="n">
-        <v>169987.02</v>
-      </c>
+        <v>37656.38</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>169987.02</v>
+        <v>13676.35</v>
       </c>
     </row>
     <row r="9">
@@ -833,15 +815,15 @@
         <v>9456627</v>
       </c>
       <c r="B9" t="n">
-        <v>1511</v>
+        <v>1401</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>243900.6</v>
+        <v>2400949</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -849,75 +831,75 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>172000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="n">
-        <v>243900.6</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>2400949</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>169987.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>169987.02</v>
+      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>169987.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9468055</v>
+        <v>9456627</v>
       </c>
       <c r="B10" t="n">
-        <v>1221</v>
+        <v>1511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>298061.56</v>
+        <v>243900.6</v>
       </c>
       <c r="E10" t="n">
-        <v>237715.09</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>201064.33</v>
-      </c>
-      <c r="G10" t="n">
-        <v>31325.06</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9651.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9651.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>288409.96</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>26472.9</v>
-      </c>
-      <c r="P10" t="n">
-        <v>26472.9</v>
-      </c>
+        <v>243900.6</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>227537.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -925,24 +907,24 @@
         <v>9468055</v>
       </c>
       <c r="B11" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>264953.82</v>
+        <v>298061.56</v>
       </c>
       <c r="E11" t="n">
-        <v>231894.37</v>
+        <v>237715.09</v>
       </c>
       <c r="F11" t="n">
-        <v>172455.6</v>
+        <v>201064.33</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>31325.06</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -951,28 +933,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>9651.6</v>
       </c>
       <c r="M11" t="n">
-        <v>264953.82</v>
+        <v>288409.96</v>
       </c>
       <c r="N11" t="n">
-        <v>23722.79</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>26472.9</v>
       </c>
       <c r="P11" t="n">
-        <v>23722.79</v>
+        <v>26472.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>196178.39</v>
+        <v>227537.23</v>
       </c>
     </row>
     <row r="12">
@@ -980,24 +962,24 @@
         <v>9468055</v>
       </c>
       <c r="B12" t="n">
-        <v>1481</v>
+        <v>1231</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>410943.68</v>
+        <v>264953.82</v>
       </c>
       <c r="E12" t="n">
-        <v>321827.42</v>
+        <v>231894.37</v>
       </c>
       <c r="F12" t="n">
-        <v>272313.27</v>
+        <v>172455.6</v>
       </c>
       <c r="G12" t="n">
-        <v>44810.88</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1015,19 +997,19 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>410943.68</v>
+        <v>264953.82</v>
       </c>
       <c r="N12" t="n">
-        <v>1339.42</v>
+        <v>23722.79</v>
       </c>
       <c r="O12" t="n">
-        <v>37860.38</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>39199.8</v>
+        <v>23722.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>311513.07</v>
+        <v>196178.39</v>
       </c>
     </row>
     <row r="13">
@@ -1035,24 +1017,24 @@
         <v>9468055</v>
       </c>
       <c r="B13" t="n">
-        <v>1501</v>
+        <v>1481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3974538.91</v>
+        <v>410943.68</v>
       </c>
       <c r="E13" t="n">
-        <v>2705821.89</v>
+        <v>321827.42</v>
       </c>
       <c r="F13" t="n">
-        <v>1918324.81</v>
+        <v>272313.27</v>
       </c>
       <c r="G13" t="n">
-        <v>302674.08</v>
+        <v>44810.88</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1061,28 +1043,28 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>726037.97</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3248500.94</v>
+        <v>410943.68</v>
       </c>
       <c r="N13" t="n">
-        <v>12856.3</v>
+        <v>1339.42</v>
       </c>
       <c r="O13" t="n">
-        <v>255763.76</v>
+        <v>37860.38</v>
       </c>
       <c r="P13" t="n">
-        <v>268620.06</v>
+        <v>39199.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2186944.87</v>
+        <v>311513.07</v>
       </c>
     </row>
     <row r="14">
@@ -1090,24 +1072,24 @@
         <v>9468055</v>
       </c>
       <c r="B14" t="n">
-        <v>4251</v>
+        <v>1501</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>422138.72</v>
+        <v>3974538.91</v>
       </c>
       <c r="E14" t="n">
-        <v>334715.09</v>
+        <v>2705821.89</v>
       </c>
       <c r="F14" t="n">
-        <v>281848.69</v>
+        <v>2215565.74</v>
       </c>
       <c r="G14" t="n">
-        <v>46987.59</v>
+        <v>302674.08</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1116,53 +1098,53 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>422138.72</v>
+        <v>3248500.94</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>12856.3</v>
       </c>
       <c r="O14" t="n">
-        <v>39709.36</v>
+        <v>255763.76</v>
       </c>
       <c r="P14" t="n">
-        <v>39709.36</v>
+        <v>268620.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>321558.05</v>
+        <v>2484185.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9468057</v>
+        <v>9468055</v>
       </c>
       <c r="B15" t="n">
-        <v>1371</v>
+        <v>4251</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7216216.2</v>
+        <v>422138.72</v>
       </c>
       <c r="E15" t="n">
-        <v>6607411.69</v>
+        <v>334715.09</v>
       </c>
       <c r="F15" t="n">
-        <v>5579292.92</v>
+        <v>281848.69</v>
       </c>
       <c r="G15" t="n">
-        <v>565340.29</v>
+        <v>46987.59</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1180,44 +1162,44 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7216216.2</v>
+        <v>422138.72</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="P15" t="n">
-        <v>476940.26</v>
+        <v>39709.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>6056233.18</v>
+        <v>321558.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9470658</v>
+        <v>9468057</v>
       </c>
       <c r="B16" t="n">
-        <v>1231</v>
+        <v>1371</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2592199.31</v>
+        <v>7216216.2</v>
       </c>
       <c r="E16" t="n">
-        <v>296909.12</v>
+        <v>6607411.69</v>
       </c>
       <c r="F16" t="n">
-        <v>296909.12</v>
+        <v>5579292.92</v>
       </c>
       <c r="G16" t="n">
-        <v>572010.63</v>
+        <v>565340.29</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1226,53 +1208,53 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>35398.54</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>35398.54</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2556800.77</v>
+        <v>7216216.2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>552155.25</v>
+        <v>476940.26</v>
       </c>
       <c r="P16" t="n">
-        <v>552155.25</v>
+        <v>476940.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>849064.37</v>
+        <v>6056233.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9473170</v>
+        <v>9470658</v>
       </c>
       <c r="B17" t="n">
-        <v>2301</v>
+        <v>1231</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>736365.61</v>
+        <v>2592199.31</v>
       </c>
       <c r="E17" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="F17" t="n">
-        <v>350401.39</v>
+        <v>296909.12</v>
       </c>
       <c r="G17" t="n">
-        <v>188341.65</v>
+        <v>572010.63</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1281,53 +1263,53 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>197622.57</v>
+        <v>35398.54</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>197622.57</v>
+        <v>35398.54</v>
       </c>
       <c r="M17" t="n">
-        <v>538743.04</v>
+        <v>2556800.77</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>188341.65</v>
+        <v>552155.25</v>
       </c>
       <c r="P17" t="n">
-        <v>188341.65</v>
+        <v>552155.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>538743.04</v>
+        <v>849064.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9473171</v>
+        <v>9473170</v>
       </c>
       <c r="B18" t="n">
-        <v>1221</v>
+        <v>2301</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14784813.95</v>
+        <v>736365.61</v>
       </c>
       <c r="E18" t="n">
-        <v>3554388.94</v>
+        <v>350401.39</v>
       </c>
       <c r="F18" t="n">
-        <v>3551283.94</v>
+        <v>350401.39</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1336,53 +1318,53 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>197622.57</v>
       </c>
       <c r="M18" t="n">
-        <v>14784813.95</v>
+        <v>538743.04</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>188341.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3551283.94</v>
+        <v>538743.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9474703</v>
+        <v>9473171</v>
       </c>
       <c r="B19" t="n">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79058892.34999999</v>
+        <v>14784813.95</v>
       </c>
       <c r="E19" t="n">
-        <v>78541892.26000001</v>
+        <v>3554388.94</v>
       </c>
       <c r="F19" t="n">
-        <v>77547634.67</v>
+        <v>3551283.94</v>
       </c>
       <c r="G19" t="n">
-        <v>517000</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1391,87 +1373,105 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>79058892.26000001</v>
+        <v>14784813.95</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>509950</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>509950</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>78057584.67</v>
+        <v>3551283.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9480259</v>
+        <v>9474703</v>
       </c>
       <c r="B20" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8534591.699999999</v>
+        <v>79058892.34999999</v>
       </c>
       <c r="E20" t="n">
-        <v>8436908.5</v>
+        <v>78541892.26000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8437270.5</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+        <v>77547634.67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>517000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.09</v>
+      </c>
       <c r="M20" t="n">
-        <v>8534591.699999999</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+        <v>79058892.26000001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>509950</v>
+      </c>
+      <c r="P20" t="n">
+        <v>509950</v>
+      </c>
       <c r="Q20" t="n">
-        <v>8437270.5</v>
+        <v>78057584.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9493230</v>
+        <v>9480259</v>
       </c>
       <c r="B21" t="n">
-        <v>1071</v>
+        <v>1221</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3500000</v>
+        <v>8534591.699999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>8436908.5</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>8437270.5</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1480,18 +1480,18 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>3500000</v>
+        <v>8534591.699999999</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8437270.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9493391</v>
+        <v>9493230</v>
       </c>
       <c r="B22" t="n">
         <v>1071</v>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1517,7 +1517,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1528,24 +1528,24 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9501917</v>
+        <v>9493391</v>
       </c>
       <c r="B23" t="n">
-        <v>1491</v>
+        <v>1071</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7500000</v>
+        <v>11399338.2</v>
       </c>
       <c r="E23" t="n">
-        <v>7500000</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>3750000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1554,12 +1554,86 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>7500000</v>
+        <v>11399338.2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9501912</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1301</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14924854.53</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14924854.53</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4477456.36</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>14924854.53</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>4477456.36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9501917</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1491</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
         <v>3750000</v>
       </c>
     </row>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -571,7 +571,7 @@
         <v>209101.99</v>
       </c>
       <c r="F3" t="n">
-        <v>133252.22</v>
+        <v>209101.99</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -586,7 +586,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>133252.22</v>
+        <v>209101.99</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>5971783.16</v>
       </c>
       <c r="F4" t="n">
-        <v>5443523.17</v>
+        <v>5471783.16</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -623,7 +623,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5443523.17</v>
+        <v>5471783.16</v>
       </c>
     </row>
     <row r="5">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>328550512.49</v>
+        <v>331216339.07</v>
       </c>
       <c r="E7" t="n">
-        <v>145099795.85</v>
+        <v>147906921.36</v>
       </c>
       <c r="F7" t="n">
-        <v>135223103.73</v>
+        <v>137296327.58</v>
       </c>
       <c r="G7" t="n">
         <v>17110597.25</v>
@@ -758,7 +758,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>317924794.88</v>
+        <v>320590621.46</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
@@ -770,7 +770,7 @@
         <v>20635321.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>155858424.79</v>
+        <v>157931648.64</v>
       </c>
     </row>
     <row r="8">
@@ -792,7 +792,7 @@
         <v>37656.38</v>
       </c>
       <c r="F8" t="n">
-        <v>13676.35</v>
+        <v>26182.28</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -807,7 +807,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>13676.35</v>
+        <v>26182.28</v>
       </c>
     </row>
     <row r="9">
@@ -881,7 +881,7 @@
         <v>243900.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7064.85</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>264953.82</v>
+        <v>270953.82</v>
       </c>
       <c r="E12" t="n">
         <v>231894.37</v>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>264953.82</v>
+        <v>270953.82</v>
       </c>
       <c r="N12" t="n">
         <v>23722.79</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3974538.91</v>
+        <v>3974577.17</v>
       </c>
       <c r="E14" t="n">
-        <v>2705821.89</v>
+        <v>2705860.15</v>
       </c>
       <c r="F14" t="n">
-        <v>2215565.74</v>
+        <v>2215604</v>
       </c>
       <c r="G14" t="n">
         <v>302674.08</v>
@@ -1107,7 +1107,7 @@
         <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3248500.94</v>
+        <v>3248539.2</v>
       </c>
       <c r="N14" t="n">
         <v>12856.3</v>
@@ -1119,7 +1119,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>2484185.8</v>
+        <v>2484224.06</v>
       </c>
     </row>
     <row r="15">
@@ -1468,10 +1468,10 @@
         <v>8534591.699999999</v>
       </c>
       <c r="E21" t="n">
-        <v>8436908.5</v>
+        <v>8438645.300000001</v>
       </c>
       <c r="F21" t="n">
-        <v>8437270.5</v>
+        <v>8439007.300000001</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>8437270.5</v>
+        <v>8439007.300000001</v>
       </c>
     </row>
     <row r="22">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9350820</v>
+        <v>9360945</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>9350820</v>
+        <v>9360945</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>331216339.07</v>
+        <v>331548013.12</v>
       </c>
       <c r="E7" t="n">
-        <v>147906921.36</v>
+        <v>150581855.19</v>
       </c>
       <c r="F7" t="n">
-        <v>137296327.58</v>
+        <v>142082857.64</v>
       </c>
       <c r="G7" t="n">
         <v>17110597.25</v>
@@ -758,19 +758,19 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>320590621.46</v>
+        <v>320922295.51</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
       </c>
       <c r="O7" t="n">
-        <v>15605881.05</v>
+        <v>16921421.39</v>
       </c>
       <c r="P7" t="n">
-        <v>20635321.06</v>
+        <v>21950861.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>157931648.64</v>
+        <v>164033719.04</v>
       </c>
     </row>
     <row r="8">
@@ -792,7 +792,7 @@
         <v>37656.38</v>
       </c>
       <c r="F8" t="n">
-        <v>26182.28</v>
+        <v>26623.94</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -807,7 +807,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>26182.28</v>
+        <v>26623.94</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>243900.6</v>
       </c>
       <c r="E10" t="n">
+        <v>15161.15</v>
+      </c>
+      <c r="F10" t="n">
         <v>7064.85</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -899,7 +899,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7064.85</v>
       </c>
     </row>
     <row r="11">
@@ -973,7 +973,7 @@
         <v>270953.82</v>
       </c>
       <c r="E12" t="n">
-        <v>231894.37</v>
+        <v>264560.43</v>
       </c>
       <c r="F12" t="n">
         <v>172455.6</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3974577.17</v>
+        <v>4459670.57</v>
       </c>
       <c r="E14" t="n">
-        <v>2705860.15</v>
+        <v>2705090.15</v>
       </c>
       <c r="F14" t="n">
         <v>2215604</v>
@@ -1107,7 +1107,7 @@
         <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3248539.2</v>
+        <v>3733632.6</v>
       </c>
       <c r="N14" t="n">
         <v>12856.3</v>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7216216.2</v>
+        <v>8311574.75</v>
       </c>
       <c r="E16" t="n">
-        <v>6607411.69</v>
+        <v>7746132.71</v>
       </c>
       <c r="F16" t="n">
         <v>5579292.92</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7216216.2</v>
+        <v>8311574.75</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1263,16 +1263,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>35398.54</v>
+        <v>1383748.21</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>35398.54</v>
+        <v>1383748.21</v>
       </c>
       <c r="M17" t="n">
-        <v>2556800.77</v>
+        <v>1208451.1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>3551283.94</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>628366.4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>628366.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>628366.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>3551283.94</v>
+        <v>4179650.34</v>
       </c>
     </row>
     <row r="20">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>331548013.12</v>
+        <v>331547921.56</v>
       </c>
       <c r="E7" t="n">
-        <v>150581855.19</v>
+        <v>151191358.02</v>
       </c>
       <c r="F7" t="n">
         <v>142082857.64</v>
@@ -758,7 +758,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>320922295.51</v>
+        <v>320922203.95</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4459670.57</v>
+        <v>4485670.57</v>
       </c>
       <c r="E14" t="n">
         <v>2705090.15</v>
@@ -1107,7 +1107,7 @@
         <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3733632.6</v>
+        <v>3759632.6</v>
       </c>
       <c r="N14" t="n">
         <v>12856.3</v>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>209101.99</v>
+        <v>219101.99</v>
       </c>
       <c r="E3" t="n">
         <v>209101.99</v>
@@ -580,7 +580,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>209101.99</v>
+        <v>219101.99</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>331547921.56</v>
+        <v>331547914.11</v>
       </c>
       <c r="E7" t="n">
         <v>151191358.02</v>
       </c>
       <c r="F7" t="n">
-        <v>142082857.64</v>
+        <v>144555558.98</v>
       </c>
       <c r="G7" t="n">
         <v>17110597.25</v>
@@ -758,7 +758,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>320922203.95</v>
+        <v>320922196.5</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
@@ -770,7 +770,7 @@
         <v>21950861.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>164033719.04</v>
+        <v>166506420.38</v>
       </c>
     </row>
     <row r="8">
@@ -881,10 +881,10 @@
         <v>243900.6</v>
       </c>
       <c r="E10" t="n">
-        <v>15161.15</v>
+        <v>19631.15</v>
       </c>
       <c r="F10" t="n">
-        <v>7064.85</v>
+        <v>7950.4</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -899,7 +899,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>7064.85</v>
+        <v>7950.4</v>
       </c>
     </row>
     <row r="11">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>298061.56</v>
+        <v>332397.92</v>
       </c>
       <c r="E11" t="n">
-        <v>237715.09</v>
+        <v>272051.45</v>
       </c>
       <c r="F11" t="n">
-        <v>201064.33</v>
+        <v>230151.2</v>
       </c>
       <c r="G11" t="n">
         <v>31325.06</v>
@@ -942,7 +942,7 @@
         <v>9651.6</v>
       </c>
       <c r="M11" t="n">
-        <v>288409.96</v>
+        <v>322746.32</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>26472.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>227537.23</v>
+        <v>256624.1</v>
       </c>
     </row>
     <row r="12">
@@ -973,10 +973,10 @@
         <v>270953.82</v>
       </c>
       <c r="E12" t="n">
-        <v>264560.43</v>
+        <v>266157.21</v>
       </c>
       <c r="F12" t="n">
-        <v>172455.6</v>
+        <v>201480.56</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>23722.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>196178.39</v>
+        <v>225203.35</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>410943.68</v>
+        <v>462446.22</v>
       </c>
       <c r="E13" t="n">
         <v>321827.42</v>
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>410943.68</v>
+        <v>462446.22</v>
       </c>
       <c r="N13" t="n">
         <v>1339.42</v>
@@ -1083,7 +1083,7 @@
         <v>4485670.57</v>
       </c>
       <c r="E14" t="n">
-        <v>2705090.15</v>
+        <v>3144337.23</v>
       </c>
       <c r="F14" t="n">
         <v>2215604</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>422138.72</v>
+        <v>473642.26</v>
       </c>
       <c r="E15" t="n">
         <v>334715.09</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>422138.72</v>
+        <v>473642.26</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>7746132.71</v>
       </c>
       <c r="F16" t="n">
-        <v>5579292.92</v>
+        <v>6541502.76</v>
       </c>
       <c r="G16" t="n">
         <v>565340.29</v>
@@ -1229,7 +1229,7 @@
         <v>476940.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>6056233.18</v>
+        <v>7018443.02</v>
       </c>
     </row>
     <row r="17">
@@ -1254,7 +1254,7 @@
         <v>296909.12</v>
       </c>
       <c r="G17" t="n">
-        <v>572010.63</v>
+        <v>846691.64</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1278,13 +1278,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>552155.25</v>
+        <v>813651.58</v>
       </c>
       <c r="P17" t="n">
-        <v>552155.25</v>
+        <v>813651.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>849064.37</v>
+        <v>1110560.7</v>
       </c>
     </row>
     <row r="18">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14784813.95</v>
+        <v>14827285.96</v>
       </c>
       <c r="E19" t="n">
         <v>3554388.94</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>14784813.95</v>
+        <v>14827285.96</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8534591.699999999</v>
+        <v>8544783.470000001</v>
       </c>
       <c r="E21" t="n">
         <v>8438645.300000001</v>
@@ -1480,7 +1480,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>8534591.699999999</v>
+        <v>8544783.470000001</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219101.99</v>
+        <v>281298.01</v>
       </c>
       <c r="E3" t="n">
-        <v>209101.99</v>
+        <v>211388.31</v>
       </c>
       <c r="F3" t="n">
         <v>209101.99</v>
@@ -580,7 +580,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>219101.99</v>
+        <v>281298.01</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5973853.61</v>
+        <v>6002186.96</v>
       </c>
       <c r="E4" t="n">
         <v>5971783.16</v>
@@ -617,7 +617,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>5973853.61</v>
+        <v>6002186.96</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -734,7 +734,7 @@
         <v>331547914.11</v>
       </c>
       <c r="E7" t="n">
-        <v>151191358.02</v>
+        <v>157357220.15</v>
       </c>
       <c r="F7" t="n">
         <v>144555558.98</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37656.38</v>
+        <v>50432.87</v>
       </c>
       <c r="E8" t="n">
         <v>37656.38</v>
@@ -801,7 +801,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>37656.38</v>
+        <v>50432.87</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -881,10 +881,10 @@
         <v>243900.6</v>
       </c>
       <c r="E10" t="n">
-        <v>19631.15</v>
+        <v>34356.83</v>
       </c>
       <c r="F10" t="n">
-        <v>7950.4</v>
+        <v>29699.37</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -899,7 +899,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>7950.4</v>
+        <v>29699.37</v>
       </c>
     </row>
     <row r="11">
@@ -1028,7 +1028,7 @@
         <v>462446.22</v>
       </c>
       <c r="E13" t="n">
-        <v>321827.42</v>
+        <v>373331.96</v>
       </c>
       <c r="F13" t="n">
         <v>272313.27</v>
@@ -1083,10 +1083,10 @@
         <v>4485670.57</v>
       </c>
       <c r="E14" t="n">
-        <v>3144337.23</v>
+        <v>3144825.63</v>
       </c>
       <c r="F14" t="n">
-        <v>2215604</v>
+        <v>2599382.61</v>
       </c>
       <c r="G14" t="n">
         <v>302674.08</v>
@@ -1119,7 +1119,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>2484224.06</v>
+        <v>2868002.67</v>
       </c>
     </row>
     <row r="15">
@@ -1138,7 +1138,7 @@
         <v>473642.26</v>
       </c>
       <c r="E15" t="n">
-        <v>334715.09</v>
+        <v>385645.46</v>
       </c>
       <c r="F15" t="n">
         <v>281848.69</v>
@@ -1254,7 +1254,7 @@
         <v>296909.12</v>
       </c>
       <c r="G17" t="n">
-        <v>846691.64</v>
+        <v>911541.98</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1278,13 +1278,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>813651.58</v>
+        <v>878501.92</v>
       </c>
       <c r="P17" t="n">
-        <v>813651.58</v>
+        <v>878501.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>1110560.7</v>
+        <v>1175411.04</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14827285.96</v>
+        <v>14834590.66</v>
       </c>
       <c r="E19" t="n">
-        <v>3554388.94</v>
+        <v>3734860.96</v>
       </c>
       <c r="F19" t="n">
-        <v>3551283.94</v>
+        <v>3731755.96</v>
       </c>
       <c r="G19" t="n">
-        <v>628366.4</v>
+        <v>1482406.4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1382,19 +1382,19 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>14827285.96</v>
+        <v>14834590.66</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>628366.4</v>
+        <v>1482406.4</v>
       </c>
       <c r="P19" t="n">
-        <v>628366.4</v>
+        <v>1482406.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4179650.34</v>
+        <v>5214162.36</v>
       </c>
     </row>
     <row r="20">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8544783.470000001</v>
+        <v>8569387.880000001</v>
       </c>
       <c r="E21" t="n">
-        <v>8438645.300000001</v>
+        <v>8487486.27</v>
       </c>
       <c r="F21" t="n">
-        <v>8439007.300000001</v>
+        <v>8487848.27</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1480,35 +1480,35 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>8544783.470000001</v>
+        <v>8569387.880000001</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>8439007.300000001</v>
+        <v>8487848.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9493230</v>
+        <v>9480440</v>
       </c>
       <c r="B22" t="n">
-        <v>1071</v>
+        <v>2241</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3500000</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1517,18 +1517,18 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>3500000</v>
+        <v>8635921.619999999</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>8635921.619999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9493391</v>
+        <v>9493230</v>
       </c>
       <c r="B23" t="n">
         <v>1071</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>11399338.2</v>
+        <v>3500000</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1565,24 +1565,24 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9501912</v>
+        <v>9493391</v>
       </c>
       <c r="B24" t="n">
-        <v>1301</v>
+        <v>1071</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14924854.53</v>
+        <v>11399338.2</v>
       </c>
       <c r="E24" t="n">
-        <v>14924854.53</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4477456.36</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1591,35 +1591,35 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>14924854.53</v>
+        <v>11399338.2</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>4477456.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9501917</v>
+        <v>9501912</v>
       </c>
       <c r="B25" t="n">
-        <v>1491</v>
+        <v>1301</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7500000</v>
+        <v>14924854.53</v>
       </c>
       <c r="E25" t="n">
-        <v>7500000</v>
+        <v>14924854.53</v>
       </c>
       <c r="F25" t="n">
-        <v>3750000</v>
+        <v>4477456.36</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1628,12 +1628,49 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>7500000</v>
+        <v>14924854.53</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
+        <v>4477456.36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9501917</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1491</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
         <v>3750000</v>
       </c>
     </row>

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -568,7 +568,7 @@
         <v>281298.01</v>
       </c>
       <c r="E3" t="n">
-        <v>211388.31</v>
+        <v>273584.33</v>
       </c>
       <c r="F3" t="n">
         <v>209101.99</v>
@@ -605,7 +605,7 @@
         <v>6002186.96</v>
       </c>
       <c r="E4" t="n">
-        <v>5971783.16</v>
+        <v>6000116.51</v>
       </c>
       <c r="F4" t="n">
         <v>5471783.16</v>
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>331547914.11</v>
+        <v>331082119.71</v>
       </c>
       <c r="E7" t="n">
-        <v>157357220.15</v>
+        <v>164485457.43</v>
       </c>
       <c r="F7" t="n">
-        <v>144555558.98</v>
+        <v>150700771.82</v>
       </c>
       <c r="G7" t="n">
-        <v>17110597.25</v>
+        <v>17505440.57</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>320922196.5</v>
+        <v>320456402.1</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
@@ -770,7 +770,7 @@
         <v>21950861.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>166506420.38</v>
+        <v>172651633.22</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         <v>50432.87</v>
       </c>
       <c r="E8" t="n">
-        <v>37656.38</v>
+        <v>50432.87</v>
       </c>
       <c r="F8" t="n">
         <v>26623.94</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>243900.6</v>
+        <v>245298.82</v>
       </c>
       <c r="E10" t="n">
         <v>34356.83</v>
       </c>
       <c r="F10" t="n">
-        <v>29699.37</v>
+        <v>34115.73</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -893,13 +893,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>243900.6</v>
+        <v>245298.82</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>29699.37</v>
+        <v>34115.73</v>
       </c>
     </row>
     <row r="11">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>270953.82</v>
+        <v>303520.57</v>
       </c>
       <c r="E12" t="n">
         <v>266157.21</v>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>270953.82</v>
+        <v>303520.57</v>
       </c>
       <c r="N12" t="n">
         <v>23722.79</v>
@@ -1031,7 +1031,7 @@
         <v>373331.96</v>
       </c>
       <c r="F13" t="n">
-        <v>272313.27</v>
+        <v>315943.56</v>
       </c>
       <c r="G13" t="n">
         <v>44810.88</v>
@@ -1064,7 +1064,7 @@
         <v>39199.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>311513.07</v>
+        <v>355143.36</v>
       </c>
     </row>
     <row r="14">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4485670.57</v>
+        <v>4485340.57</v>
       </c>
       <c r="E14" t="n">
-        <v>3144825.63</v>
+        <v>3149586.43</v>
       </c>
       <c r="F14" t="n">
-        <v>2599382.61</v>
+        <v>2604473.41</v>
       </c>
       <c r="G14" t="n">
         <v>302674.08</v>
@@ -1107,7 +1107,7 @@
         <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3759632.6</v>
+        <v>3759302.6</v>
       </c>
       <c r="N14" t="n">
         <v>12856.3</v>
@@ -1119,7 +1119,7 @@
         <v>268620.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>2868002.67</v>
+        <v>2873093.47</v>
       </c>
     </row>
     <row r="15">
@@ -1138,10 +1138,10 @@
         <v>473642.26</v>
       </c>
       <c r="E15" t="n">
-        <v>385645.46</v>
+        <v>386219.63</v>
       </c>
       <c r="F15" t="n">
-        <v>281848.69</v>
+        <v>325478.98</v>
       </c>
       <c r="G15" t="n">
         <v>46987.59</v>
@@ -1174,7 +1174,7 @@
         <v>39709.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>321558.05</v>
+        <v>365188.34</v>
       </c>
     </row>
     <row r="16">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8311574.75</v>
+        <v>9506724.99</v>
       </c>
       <c r="E16" t="n">
         <v>7746132.71</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8311574.75</v>
+        <v>9506724.99</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         <v>14834590.66</v>
       </c>
       <c r="E19" t="n">
-        <v>3734860.96</v>
+        <v>3736274.77</v>
       </c>
       <c r="F19" t="n">
-        <v>3731755.96</v>
+        <v>3733169.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1482406.4</v>
+        <v>1714032.4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1388,13 +1388,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1482406.4</v>
+        <v>1556164.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1482406.4</v>
+        <v>1556164.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>5214162.36</v>
+        <v>5289334.17</v>
       </c>
     </row>
     <row r="20">
@@ -1468,10 +1468,10 @@
         <v>8569387.880000001</v>
       </c>
       <c r="E21" t="n">
-        <v>8487486.27</v>
+        <v>8494480.630000001</v>
       </c>
       <c r="F21" t="n">
-        <v>8487848.27</v>
+        <v>8494842.630000001</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>8487848.27</v>
+        <v>8494842.630000001</v>
       </c>
     </row>
     <row r="22">

--- a/upload/orgao.xlsx
+++ b/upload/orgao.xlsx
@@ -571,7 +571,7 @@
         <v>273584.33</v>
       </c>
       <c r="F3" t="n">
-        <v>209101.99</v>
+        <v>273584.33</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -586,7 +586,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>209101.99</v>
+        <v>273584.33</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>6000116.51</v>
       </c>
       <c r="F4" t="n">
-        <v>5471783.16</v>
+        <v>5500116.51</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -623,7 +623,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5471783.16</v>
+        <v>5500116.51</v>
       </c>
     </row>
     <row r="5">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>331082119.71</v>
+        <v>331082087.64</v>
       </c>
       <c r="E7" t="n">
-        <v>164485457.43</v>
+        <v>172353813.93</v>
       </c>
       <c r="F7" t="n">
-        <v>150700771.82</v>
+        <v>159501385.8</v>
       </c>
       <c r="G7" t="n">
         <v>17505440.57</v>
@@ -758,19 +758,19 @@
         <v>10625717.61</v>
       </c>
       <c r="M7" t="n">
-        <v>320456402.1</v>
+        <v>320456370.03</v>
       </c>
       <c r="N7" t="n">
         <v>5029440.01</v>
       </c>
       <c r="O7" t="n">
-        <v>16921421.39</v>
+        <v>17316264.71</v>
       </c>
       <c r="P7" t="n">
-        <v>21950861.4</v>
+        <v>22345704.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>172651633.22</v>
+        <v>181847090.52</v>
       </c>
     </row>
     <row r="8">
@@ -792,7 +792,7 @@
         <v>50432.87</v>
       </c>
       <c r="F8" t="n">
-        <v>26623.94</v>
+        <v>39400.43</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -807,7 +807,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>26623.94</v>
+        <v>39400.43</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>245298.82</v>
+        <v>287221.89</v>
       </c>
       <c r="E10" t="n">
-        <v>34356.83</v>
+        <v>123303.87</v>
       </c>
       <c r="F10" t="n">
         <v>34115.73</v>
@@ -893,7 +893,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>245298.82</v>
+        <v>287221.89</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>332397.92</v>
+        <v>364747.57</v>
       </c>
       <c r="E11" t="n">
         <v>272051.45</v>
@@ -942,7 +942,7 @@
         <v>9651.6</v>
       </c>
       <c r="M11" t="n">
-        <v>322746.32</v>
+        <v>355095.97</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>303520.57</v>
       </c>
       <c r="E12" t="n">
-        <v>266157.21</v>
+        <v>300305.3</v>
       </c>
       <c r="F12" t="n">
-        <v>201480.56</v>
+        <v>230397.28</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>23722.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>225203.35</v>
+        <v>254120.07</v>
       </c>
     </row>
     <row r="13">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4485340.57</v>
+        <v>4975571.29</v>
       </c>
       <c r="E14" t="n">
-        <v>3149586.43</v>
+        <v>3149717.88</v>
       </c>
       <c r="F14" t="n">
         <v>2604473.41</v>
@@ -1107,7 +1107,7 @@
         <v>726037.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3759302.6</v>
+        <v>4249533.32</v>
       </c>
       <c r="N14" t="n">
         <v>12856.3</v>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9506724.99</v>
+        <v>9593274.119999999</v>
       </c>
       <c r="E16" t="n">
-        <v>7746132.71</v>
+        <v>9027832.08</v>
       </c>
       <c r="F16" t="n">
         <v>6541502.76</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>9506724.99</v>
+        <v>9593274.119999999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14834590.66</v>
+        <v>14891992.87</v>
       </c>
       <c r="E19" t="n">
         <v>3736274.77</v>
@@ -1364,7 +1364,7 @@
         <v>3733169.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1714032.4</v>
+        <v>2101197.2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1382,19 +1382,19 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>14834590.66</v>
+        <v>14891992.87</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1556164.4</v>
+        <v>2071339.96</v>
       </c>
       <c r="P19" t="n">
-        <v>1556164.4</v>
+        <v>2071339.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>5289334.17</v>
+        <v>5804509.73</v>
       </c>
     </row>
     <row r="20">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8569387.880000001</v>
+        <v>8604166.130000001</v>
       </c>
       <c r="E21" t="n">
         <v>8494480.630000001</v>
@@ -1480,7 +1480,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>8569387.880000001</v>
+        <v>8604166.130000001</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
